--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>516300</v>
+      </c>
+      <c r="E8" s="3">
         <v>494600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>462600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>534400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>824600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>965300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>838700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>786600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>745100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>524600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>395600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>375500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>320000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>274800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>192800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>353300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>423100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E9" s="3">
         <v>174100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>175000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>185800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>186500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>209400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>178000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>159900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>150600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>139900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>129600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>140000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>138500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>114100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>115300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>177200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>185500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E10" s="3">
         <v>320500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>287600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>348600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>638100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>755900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>660700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>626700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>594500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>384700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>266000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>235500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>181500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>160700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>77500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>176100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>237600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +945,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1002,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,23 +1061,26 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1021700</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-12500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-432600</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1069,96 +1088,102 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-192100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-23900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-22200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-610800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-662900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>47800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>69700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1564900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>46100</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E15" s="3">
         <v>151100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>154400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>148100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>171900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>130200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>140800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>134200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>148200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>167800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>149700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>106000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>148200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>167700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>106700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>157800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>139900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1502100</v>
+      </c>
+      <c r="E17" s="3">
         <v>404600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>378900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>-15100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>417300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>388500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>373700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>319000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>332500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-279500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-366300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>338200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>375000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>341400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1956800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>422700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-985800</v>
+      </c>
+      <c r="E18" s="3">
         <v>90000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>83700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>549500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>407300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>576800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>465000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>619200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>426100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>192100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>675100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>741800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-148600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,288 +1342,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>117700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-140100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>477200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-141200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>53700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-324100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-376900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-139300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-51300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-14200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>47500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>57300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>37200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-633200</v>
+      </c>
+      <c r="E21" s="3">
         <v>239400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>355700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>557600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1056400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>565900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>659500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>429300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>561700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>685500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>796500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>115800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>177500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>20200</v>
+        <v>22900</v>
       </c>
       <c r="E22" s="3">
         <v>20200</v>
       </c>
       <c r="F22" s="3">
+        <v>20200</v>
+      </c>
+      <c r="G22" s="3">
         <v>21900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>21100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-915100</v>
+      </c>
+      <c r="E23" s="3">
         <v>68100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>181100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>387600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>862000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>411200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>497600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>280200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>397200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-203500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>517000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>671300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-52200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-119000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E24" s="3">
         <v>10800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>53200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>466600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>140100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>135000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>52600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-56400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>171300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-70000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-47700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-247700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-803100</v>
+      </c>
+      <c r="E26" s="3">
         <v>57300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>127900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>380300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>395400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>271100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>362600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>284000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>344600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-147100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>451300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-57700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-69900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-71300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-803100</v>
+      </c>
+      <c r="E27" s="3">
         <v>57300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>127900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>380300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>395400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>271100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>362600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>284000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>344600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-147100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>451300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-57700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-69900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-71300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-117700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>140100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-477200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>141200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-53700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>324100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>376900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>139300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>51300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>14200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>22300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-47500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-57300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-37200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-803100</v>
+      </c>
+      <c r="E33" s="3">
         <v>57300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>127900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>380300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>395400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>271100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>362600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>284000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>344600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-147100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>451300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-57700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-69900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-71300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-803100</v>
+      </c>
+      <c r="E35" s="3">
         <v>57300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>127900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>380300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>395400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>271100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>362600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>284000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>344600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-147100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>451300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-57700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-69900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-71300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,78 +2396,82 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>140800</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>50600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
         <v>3600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>29000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="3">
+        <v>700</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E42" s="3">
-        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
+      <c r="G42" s="3">
+        <v>100</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>8</v>
@@ -2399,8 +2488,8 @@
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2423,255 +2512,270 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>242900</v>
+      </c>
+      <c r="E43" s="3">
         <v>301700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>287900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>334600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>373700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>391200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>369400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>396700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>328600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>281600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>205900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>240500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>196100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>179400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>233000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>188400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>211400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E44" s="3">
         <v>26900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>30700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>19700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>20100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>24600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>17100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>21500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>15800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>29400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>381800</v>
+      </c>
+      <c r="E45" s="3">
         <v>328600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>383600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>388800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>307300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>168700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>134200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>126800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>118200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>155800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>58300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>65800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>83100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>123900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>77900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>823500</v>
+      </c>
+      <c r="E46" s="3">
         <v>657300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>743500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>854000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>714400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>598500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>530100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>551900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>472800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>460100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>292800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>300000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>261000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>267600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>342400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>344700</v>
-      </c>
-      <c r="S46" s="3">
-        <v>347700</v>
       </c>
       <c r="T46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E47" s="3">
         <v>68300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>58600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>52100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>56400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>38100</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2688,8 +2792,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2703,64 +2807,70 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5080900</v>
+      </c>
+      <c r="E48" s="3">
         <v>6282900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6235400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6226800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5962100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5646000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5421300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5175200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5057500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4915500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4816300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4071700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3361200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3352000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3553000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3531500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5301800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,64 +3043,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>258200</v>
+      </c>
+      <c r="E52" s="3">
         <v>152700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>142400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>152200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>258100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>316300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>292100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>472000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>375000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>374000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>298400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>354800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>486900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>506800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>466700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>496200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>216700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3161,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6235800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7161200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7180000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7285200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6991100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6608600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6281600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6199100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5905300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5749600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5407500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4726500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4109100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4126400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4362100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4372300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5866100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3268,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>380400</v>
+      </c>
+      <c r="E57" s="3">
         <v>368700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>428500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>469900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>481400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>444700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>422800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>398900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>440700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>364500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>346500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>312000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>297700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>246700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>309600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>441800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>312400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3251,232 +3384,247 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>315700</v>
+      </c>
+      <c r="E59" s="3">
         <v>364800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>442200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>564500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>410600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>542300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>535800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>655900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>306200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>531500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>181700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>73300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>135500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>58800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>64500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>103800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>696100</v>
+      </c>
+      <c r="E60" s="3">
         <v>733400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>870800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1034400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>892000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>987100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>958700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1054900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>746800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>896000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>528200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>385300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>433100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>330900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>368400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>506300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>416200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>947000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1003300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>954700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>979900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1132900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1463400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1579300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1436100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1711800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1827400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1841500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1984200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2010400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2153200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2220700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2085300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2017700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1561100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1572100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1531500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1491300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1565100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1268100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1062100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1379600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1380600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1290800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1176000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>946500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>740200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>663200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>742300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>628400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>978900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3797,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3204200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3308800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3357000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3505500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3590000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3718600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3600100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3870600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3839200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4014300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3545700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3315900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3183700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3147300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3331400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3220000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3412800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4115,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1263600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-458100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-503500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-626700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4351,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3031600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3852400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3823000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3779700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3401100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2889900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2681500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2328500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2066100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1735400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1861800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1410600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>925400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>979100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1030700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1152300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2453300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-803100</v>
+      </c>
+      <c r="E81" s="3">
         <v>57300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>127900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>380300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>395400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>271100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>362600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>284000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>344600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-147100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>451300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-57700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-69900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-71300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4617,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E83" s="3">
         <v>151100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>154400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>148100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>171900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>130200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>140800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>134200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>148200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>167800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>149700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>106000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>148200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>167700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>106700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>157800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>139900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>343800</v>
+      </c>
+      <c r="E89" s="3">
         <v>118400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>173600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>388600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>495200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>447600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>530400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>341100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>250400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>211500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>253400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>119100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>135100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>93800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>278400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>220500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-145600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-128800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-169000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-289000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-172900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-186200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-611000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-92100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-172700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-158600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-132900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-170400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-164400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-108700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-168100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-168300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-612600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-110300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-134900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-162900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-97200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-74700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-50600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-41800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-122000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-187000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-117000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5312,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5089,20 +5322,20 @@
         <v>-16400</v>
       </c>
       <c r="E96" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F96" s="3">
         <v>-16200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-13100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-13000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-10000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -5125,19 +5358,22 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-17400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-100300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-97300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5546,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-45200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-194200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-323000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-272500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>78500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-231400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-108000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-48400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-159900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-47200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-83200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>118200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-104400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-85200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-50700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-49100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>86000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,275 +656,288 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>497900</v>
+      </c>
+      <c r="E8" s="3">
         <v>516300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>494600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>462600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>534400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>824600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>965300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>838700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>786600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>745100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>524600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>395600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>375500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>320000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>274800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>192800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>353300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>423100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>187700</v>
+      </c>
+      <c r="E9" s="3">
         <v>155400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>174100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>175000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>185800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>186500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>209400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>178000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>159900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>150600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>139900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>129600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>140000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>138500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>114100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>115300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>177200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>185500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>310200</v>
+      </c>
+      <c r="E10" s="3">
         <v>360900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>320500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>287600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>348600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>638100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>755900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>660700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>626700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>594500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>384700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>266000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>235500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>181500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>160700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>77500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>176100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>237600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -946,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1005,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,26 +1081,29 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1021700</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-12500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-432600</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1091,99 +1111,105 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-192100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-23900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-22200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-610800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-662900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>47800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>69700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1564900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>46100</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>178400</v>
+      </c>
+      <c r="E15" s="3">
         <v>259000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>151100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>154400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>148100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>171900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>130200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>140800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>134200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>148200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>167800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>149700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>106000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>148200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>167700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>106700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>157800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>139900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>436200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1502100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>404600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>378900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>-15100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>417300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>388500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>373700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>319000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>332500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-279500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-366300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>338200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>375000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>341400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1956800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>422700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>61700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-985800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>90000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>83700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>549500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>407300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>576800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>465000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>619200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>426100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>192100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>675100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>741800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-148600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,303 +1376,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E20" s="3">
         <v>93600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>117700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-140100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>477200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-141200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>53700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-324100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-12600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-376900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-139300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-51300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-22300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>47500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>57300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>37200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>252200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-633200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>239400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>355700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>557600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1056400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>565900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>659500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>429300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>561700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>685500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>796500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>115800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>177500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E22" s="3">
         <v>22900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>20200</v>
       </c>
       <c r="F22" s="3">
         <v>20200</v>
       </c>
       <c r="G22" s="3">
+        <v>20200</v>
+      </c>
+      <c r="H22" s="3">
         <v>21900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-915100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>181100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>387600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>862000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>411200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>497600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>280200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>397200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-203500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>517000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>671300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-140000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-119000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-112000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>53200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>466600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>140100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>135000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>52600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-56400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>171300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-70000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-47700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-247700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-803100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>57300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>127900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>380300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>395400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>271100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>362600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>284000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>344600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-147100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>451300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-69900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-71300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-803100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>57300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>127900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>380300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>395400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>271100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>362600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>284000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>344600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-147100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>451300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-69900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-71300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-93600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-117700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>140100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-477200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>141200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-53700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>324100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>12600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>376900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>139300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>51300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>14200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>22300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-47500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-57300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-37200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-803100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>57300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>127900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>380300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>395400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>271100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>362600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>284000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>344600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-147100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>451300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-69900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-71300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-803100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>57300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>127900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>380300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>395400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>271100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>362600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>284000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>344600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-147100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>451300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-69900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-71300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,84 +2483,88 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E41" s="3">
         <v>140800</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>50600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6000</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
       <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>3600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F42" s="3">
-        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
+      <c r="H42" s="3">
+        <v>100</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>8</v>
@@ -2491,8 +2581,8 @@
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2515,270 +2605,285 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>365200</v>
+      </c>
+      <c r="E43" s="3">
         <v>242900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>301700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>287900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>334600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>373700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>391200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>369400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>396700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>328600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>281600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>205900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>240500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>196100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>179400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>233000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>188400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>211400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E44" s="3">
         <v>57300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>30700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>30800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>25800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>20100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>22800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>28500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>24600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>17100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>21500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>15800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>29400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>234200</v>
+      </c>
+      <c r="E45" s="3">
         <v>381800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>328600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>383600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>388800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>307300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>168700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>134200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>126800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>118200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>155800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>44600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>65800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>83100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>123900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>77900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>886400</v>
+      </c>
+      <c r="E46" s="3">
         <v>823500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>657300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>743500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>854000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>714400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>598500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>530100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>551900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>472800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>460100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>292800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>300000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>261000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>267600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>342400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>344700</v>
-      </c>
-      <c r="T46" s="3">
-        <v>347700</v>
       </c>
       <c r="U46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E47" s="3">
         <v>73300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>58600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>52100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>56400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>47800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>38100</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -2795,8 +2900,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2810,67 +2915,73 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5140400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5080900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6282900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6235400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6226800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5962100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5646000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5421300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5175200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5057500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4915500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4816300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4071700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3361200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3352000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3553000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3531500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5301800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,67 +3163,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E52" s="3">
         <v>258200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>152700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>142400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>152200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>258100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>316300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>292100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>472000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>375000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>374000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>298400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>354800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>486900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>506800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>466700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>496200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>216700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6324600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6235800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7161200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7180000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7285200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6991100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6608600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6281600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6199100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5905300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5749600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5407500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4726500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4109100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4126400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4362100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4372300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5866100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,67 +3399,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>406300</v>
+      </c>
+      <c r="E57" s="3">
         <v>380400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>368700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>428500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>469900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>481400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>444700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>422800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>398900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>440700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>364500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>346500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>312000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>297700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>246700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>309600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>441800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>312400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3387,244 +3521,259 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>360900</v>
+      </c>
+      <c r="E59" s="3">
         <v>315700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>364800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>442200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>564500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>410600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>542300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>535800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>655900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>306200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>531500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>181700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>73300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>84200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>58800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>64500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>103800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>767200</v>
+      </c>
+      <c r="E60" s="3">
         <v>696100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>733400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>870800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1034400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>892000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>987100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>958700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1054900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>746800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>896000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>528200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>385300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>433100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>330900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>368400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>506300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>416200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>962400</v>
+      </c>
+      <c r="E61" s="3">
         <v>947000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1003300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>954700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>979900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1132900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1463400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1579300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1436100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1711800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1827400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1841500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1984200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2010400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2153200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2220700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2085300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2017700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1612800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1561100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1572100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1531500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1491300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1565100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1268100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1062100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1379600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1380600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1290800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1176000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>946500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>740200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>663200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>742300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>628400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>978900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3342400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3204200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3308800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3357000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3505500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3590000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3718600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3600100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3870600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3839200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4014300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3545700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3315900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3183700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3147300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3331400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3220000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3412800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1254600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1263600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-458100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-503500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-626700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2982200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3031600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3852400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3823000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3779700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3401100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2889900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2681500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2328500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2066100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1735400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1861800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1410600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>925400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>979100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1030700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1152300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2453300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-803100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>57300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>127900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>380300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>395400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>271100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>362600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>284000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>344600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-147100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>451300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-69900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-71300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4816,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>178400</v>
+      </c>
+      <c r="E83" s="3">
         <v>259000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>151100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>154400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>148100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>171900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>130200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>140800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>134200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>148200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>167800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>149700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>106000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>148200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>167700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>106700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>157800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>139900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>354300</v>
+      </c>
+      <c r="E89" s="3">
         <v>343800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>118400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>173600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>388600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>495200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>447600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>530400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>341100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>250400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>211500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>253400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>119100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>135100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>93800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>278400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>220500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-190800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-145600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-128800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-169000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-289000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-172900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-186200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-611000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-92100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-172700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-158600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-181300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-132900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-170400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-164400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-108700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-168100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-168300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-612600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-110300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-134900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-162900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-97200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-74700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-50600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-41800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-122000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-187000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-117000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,32 +5546,33 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-16400</v>
+        <v>-16200</v>
       </c>
       <c r="E96" s="3">
         <v>-16400</v>
       </c>
       <c r="F96" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="G96" s="3">
         <v>-16200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-13100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-13000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-10000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -5361,19 +5595,22 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-17400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-100300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-97300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,181 +5792,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-60700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-81700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-45200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-194200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-323000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-272500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>78500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-231400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-159900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-47200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-83200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-51200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>118200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-104400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-85200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>12200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E102" s="3">
         <v>141500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-50700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-49100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>86000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6000</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,288 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>461000</v>
+      </c>
+      <c r="E8" s="3">
         <v>497900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>516300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>494600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>462600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>534400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>824600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>965300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>838700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>786600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>745100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>524600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>395600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>375500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>320000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>274800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>192800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>353300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>423100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E9" s="3">
         <v>187700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>155400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>174100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>175000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>185800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>186500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>209400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>178000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>159900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>150600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>139900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>129600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>140000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>138500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>114100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>115300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>177200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>185500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>292100</v>
+      </c>
+      <c r="E10" s="3">
         <v>310200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>360900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>320500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>287600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>348600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>638100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>755900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>660700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>626700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>594500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>384700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>266000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>235500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>181500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>160700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>77500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>176100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>237600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1101,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1093,20 +1113,20 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1021700</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-12500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-432600</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1114,102 +1134,108 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-192100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-23900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-22200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-610800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-662900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>47800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>69700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1564900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>46100</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E15" s="3">
         <v>178400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>259000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>151100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>154400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>148100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>171900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>130200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>140800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>134200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>148200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>167800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>149700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>106000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>148200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>167700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>106700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>157800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>139900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>411500</v>
+      </c>
+      <c r="E17" s="3">
         <v>436200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1502100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>404600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>378900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>-15100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>417300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>388500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>373700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>167400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>319000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>332500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-279500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-366300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>338200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>375000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>341400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1956800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>422700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>49500</v>
+      </c>
+      <c r="E18" s="3">
         <v>61700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-985800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>90000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>83700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>549500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>407300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>576800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>465000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>619200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>426100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>192100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>675100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>741800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-148600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,318 +1410,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-74500</v>
+      </c>
+      <c r="E20" s="3">
         <v>12100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>93600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>117700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-140100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>477200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-141200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>53700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-324100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-376900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-139300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-51300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-14200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-22300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>47500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>57300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>37200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E21" s="3">
         <v>252200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-633200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>239400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>355700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>557600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1056400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>565900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>659500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>429300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>561700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>685500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>796500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>115800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>177500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E22" s="3">
         <v>18400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>20200</v>
       </c>
       <c r="G22" s="3">
         <v>20200</v>
       </c>
       <c r="H22" s="3">
+        <v>20200</v>
+      </c>
+      <c r="I22" s="3">
         <v>21900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="E23" s="3">
         <v>55400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-915100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>68100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>181100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>387600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>862000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>411200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>497600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>280200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>397200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-203500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>517000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>671300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-140000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-119000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E24" s="3">
         <v>53100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-112000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>53200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>466600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>140100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>135000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>52600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-56400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>171300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-70000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-47700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-247700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-803100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>57300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>127900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>380300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>395400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>271100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>362600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>284000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>344600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-147100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>451300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-57700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-69900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-71300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E27" s="3">
         <v>2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-803100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>57300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>127900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>380300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>395400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>271100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>362600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>284000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>344600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-147100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>451300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-57700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-69900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-71300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-93600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-117700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>140100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-477200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>141200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-53700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>324100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>376900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>139300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>51300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>14200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>22300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-47500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-57300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-37200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E33" s="3">
         <v>2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-803100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>57300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>127900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>380300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>395400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>271100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>362600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>284000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>344600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-147100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>451300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-57700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-69900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-71300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E35" s="3">
         <v>2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-803100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>57300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>127900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>380300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>395400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>271100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>362600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>284000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>344600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-147100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>451300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-57700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-69900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-71300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,90 +2570,94 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E41" s="3">
         <v>254700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>140800</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>50600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6000</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3">
         <v>3600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>700</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="G42" s="3">
-        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
+      <c r="I42" s="3">
+        <v>100</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>8</v>
@@ -2584,8 +2674,8 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2608,285 +2698,300 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>258500</v>
+      </c>
+      <c r="E43" s="3">
         <v>365200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>242900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>301700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>287900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>334600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>373700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>391200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>369400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>396700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>328600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>281600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>205900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>240500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>196100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>179400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>233000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>188400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>211400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E44" s="3">
         <v>32400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>57300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>21300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>30800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>25800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>20100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>28500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>24600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>17100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>21500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>15800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>29400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E45" s="3">
         <v>234200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>381800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>328600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>383600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>388800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>307300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>168700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>134200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>126800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>118200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>155800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>58300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>44600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>65800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>83100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>123900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>77900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>740900</v>
+      </c>
+      <c r="E46" s="3">
         <v>886400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>823500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>657300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>743500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>854000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>714400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>598500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>530100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>551900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>472800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>460100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>292800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>300000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>261000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>267600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>342400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>344700</v>
-      </c>
-      <c r="U46" s="3">
-        <v>347700</v>
       </c>
       <c r="V46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E47" s="3">
         <v>80300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>73300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>58600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>52100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>56400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>47800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>38100</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -2903,8 +3008,8 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2918,70 +3023,76 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5188400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5140400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5080900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6282900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6235400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6226800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5962100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5646000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5421300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5175200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5057500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4915500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4816300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4071700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3361200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3352000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3553000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3531500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5301800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,70 +3283,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>173400</v>
+      </c>
+      <c r="E52" s="3">
         <v>217500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>258200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>152700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>142400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>152200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>258100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>316300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>292100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>472000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>375000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>374000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>298400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>354800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>486900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>506800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>466700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>496200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>216700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6182800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6324600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6235800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7161200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7180000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7285200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6991100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6608600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6281600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6199100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5905300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5749600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5407500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4726500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4109100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4126400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4362100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4372300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5866100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>361200</v>
+      </c>
+      <c r="E57" s="3">
         <v>406300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>380400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>368700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>428500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>469900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>481400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>444700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>422800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>398900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>440700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>364500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>346500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>312000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>297700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>246700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>309600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>441800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>312400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3524,256 +3658,271 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>318300</v>
+      </c>
+      <c r="E59" s="3">
         <v>360900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>315700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>364800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>442200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>564500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>410600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>542300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>535800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>655900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>306200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>531500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>181700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>73300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>135500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>58800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>64500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>103800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>679500</v>
+      </c>
+      <c r="E60" s="3">
         <v>767200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>696100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>733400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>870800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1034400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>892000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>987100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>958700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1054900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>746800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>896000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>528200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>385300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>433100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>330900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>368400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>506300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>416200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1008600</v>
+      </c>
+      <c r="E61" s="3">
         <v>962400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>947000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1003300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>954700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>979900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1132900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1463400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1579300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1436100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1711800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1827400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1841500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1984200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2010400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2153200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2220700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2085300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2017700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1664100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1612800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1561100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1572100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1531500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1491300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1565100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1268100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1062100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1379600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1380600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1290800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1176000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>946500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>740200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>663200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>742300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>628400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>978900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3352200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3342400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3204200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3308800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3357000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3505500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3590000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3718600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3600100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3870600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3839200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4014300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3545700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3315900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3183700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3147300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3331400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3220000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3412800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1332500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1254600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1263600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-458100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-503500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-626700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2830600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2982200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3031600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3852400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3823000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3779700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3401100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2889900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2681500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2328500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2066100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1735400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1861800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1410600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>925400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>979100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1030700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1152300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2453300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E81" s="3">
         <v>2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-803100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>57300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>127900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>380300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>395400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>271100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>362600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>284000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>344600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-147100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>451300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-57700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-69900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-71300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E83" s="3">
         <v>178400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>259000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>151100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>154400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>148100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>171900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>130200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>140800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>134200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>148200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>167800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>149700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>106000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>148200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>167700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>106700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>157800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>139900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E89" s="3">
         <v>354300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>343800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>118400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>173600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>388600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>495200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>447600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>530400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>341100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>250400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>211500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>253400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>119100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>135100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>93800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>278400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>220500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-116100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-190800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-145600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-128800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-169000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-289000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-172900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-186200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-611000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-92100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-172700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-158600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-181300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-132900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-170400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-164400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-108700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-168100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-168300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-612600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-110300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-134900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-162900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-97200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-74700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-41800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-122000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-187000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-117000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,35 +5780,36 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-16200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-16400</v>
       </c>
       <c r="F96" s="3">
         <v>-16400</v>
       </c>
       <c r="G96" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="H96" s="3">
         <v>-16200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-13100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-13000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-10000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -5598,19 +5832,22 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-17400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-100300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-97300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-99500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-60700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-81700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-45200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-194200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-323000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-272500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>78500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-231400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-108000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-48400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-159900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-47200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-83200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-51200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>118200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-104400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-85200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>12200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>113200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>141500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-50700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-49100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>86000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6000</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>461000</v>
+        <v>331100</v>
       </c>
       <c r="E8" s="3">
-        <v>497900</v>
+        <v>315900</v>
       </c>
       <c r="F8" s="3">
-        <v>516300</v>
+        <v>339300</v>
       </c>
       <c r="G8" s="3">
-        <v>494600</v>
+        <v>361800</v>
       </c>
       <c r="H8" s="3">
-        <v>462600</v>
+        <v>327700</v>
       </c>
       <c r="I8" s="3">
-        <v>534400</v>
+        <v>320500</v>
       </c>
       <c r="J8" s="3">
+        <v>358700</v>
+      </c>
+      <c r="K8" s="3">
         <v>824600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>965300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>838700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>786600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>745100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>524600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>395600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>375500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>320000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>274800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>192800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>353300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>423100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>168900</v>
+        <v>122500</v>
       </c>
       <c r="E9" s="3">
-        <v>187700</v>
+        <v>121000</v>
       </c>
       <c r="F9" s="3">
-        <v>155400</v>
+        <v>127200</v>
       </c>
       <c r="G9" s="3">
-        <v>174100</v>
+        <v>105500</v>
       </c>
       <c r="H9" s="3">
-        <v>175000</v>
+        <v>106700</v>
       </c>
       <c r="I9" s="3">
-        <v>185800</v>
+        <v>119800</v>
       </c>
       <c r="J9" s="3">
+        <v>118200</v>
+      </c>
+      <c r="K9" s="3">
         <v>186500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>209400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>178000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>159900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>150600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>139900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>129600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>140000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>138500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>114100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>115300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>177200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>185500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>292100</v>
+        <v>208600</v>
       </c>
       <c r="E10" s="3">
-        <v>310200</v>
+        <v>194900</v>
       </c>
       <c r="F10" s="3">
-        <v>360900</v>
+        <v>212100</v>
       </c>
       <c r="G10" s="3">
-        <v>320500</v>
+        <v>256300</v>
       </c>
       <c r="H10" s="3">
-        <v>287600</v>
+        <v>221000</v>
       </c>
       <c r="I10" s="3">
-        <v>348600</v>
+        <v>200700</v>
       </c>
       <c r="J10" s="3">
+        <v>240600</v>
+      </c>
+      <c r="K10" s="3">
         <v>638100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>755900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>660700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>626700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>594500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>384700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>266000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>235500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>181500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>160700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>77500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>176100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>237600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,31 +1121,34 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1021700</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-12500</v>
+        <v>99300</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
-        <v>-432600</v>
+        <v>-9500</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-152000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1137,105 +1157,111 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-192100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-23900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-22200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-610800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-662900</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>47800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>69700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1564900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>46100</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>161200</v>
+        <v>133400</v>
       </c>
       <c r="E15" s="3">
-        <v>178400</v>
+        <v>117800</v>
       </c>
       <c r="F15" s="3">
-        <v>259000</v>
+        <v>131800</v>
       </c>
       <c r="G15" s="3">
-        <v>151100</v>
+        <v>965500</v>
       </c>
       <c r="H15" s="3">
-        <v>154400</v>
+        <v>111700</v>
       </c>
       <c r="I15" s="3">
-        <v>148100</v>
+        <v>116600</v>
       </c>
       <c r="J15" s="3">
+        <v>109500</v>
+      </c>
+      <c r="K15" s="3">
         <v>171900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>130200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>140800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>134200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>148200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>167800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>149700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>106000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>148200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>167700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>106700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>157800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>139900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>411500</v>
+        <v>254800</v>
       </c>
       <c r="E17" s="3">
-        <v>436200</v>
+        <v>337400</v>
       </c>
       <c r="F17" s="3">
-        <v>1502100</v>
+        <v>270300</v>
       </c>
       <c r="G17" s="3">
-        <v>404600</v>
+        <v>940300</v>
       </c>
       <c r="H17" s="3">
-        <v>378900</v>
+        <v>247300</v>
       </c>
       <c r="I17" s="3">
-        <v>-15100</v>
+        <v>209800</v>
       </c>
       <c r="J17" s="3">
+        <v>195400</v>
+      </c>
+      <c r="K17" s="3">
         <v>417300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>388500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>373700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>319000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>332500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-279500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-366300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>338200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>375000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>341400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1956800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>422700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>49500</v>
+        <v>76400</v>
       </c>
       <c r="E18" s="3">
-        <v>61700</v>
+        <v>-21500</v>
       </c>
       <c r="F18" s="3">
-        <v>-985800</v>
+        <v>69000</v>
       </c>
       <c r="G18" s="3">
-        <v>90000</v>
+        <v>-578500</v>
       </c>
       <c r="H18" s="3">
-        <v>83700</v>
+        <v>80500</v>
       </c>
       <c r="I18" s="3">
-        <v>549500</v>
+        <v>110600</v>
       </c>
       <c r="J18" s="3">
+        <v>163300</v>
+      </c>
+      <c r="K18" s="3">
         <v>407300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>576800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>465000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>619200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>426100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>192100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>675100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>741800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-148600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,333 +1444,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-74500</v>
+        <v>9200</v>
       </c>
       <c r="E20" s="3">
-        <v>12100</v>
+        <v>-3300</v>
       </c>
       <c r="F20" s="3">
-        <v>93600</v>
+        <v>14600</v>
       </c>
       <c r="G20" s="3">
-        <v>-1600</v>
+        <v>-2200</v>
       </c>
       <c r="H20" s="3">
-        <v>117700</v>
+        <v>15100</v>
       </c>
       <c r="I20" s="3">
-        <v>-140100</v>
+        <v>-31900</v>
       </c>
       <c r="J20" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K20" s="3">
         <v>477200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-141200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>53700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-324100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-376900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-139300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-51300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-14200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-22300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>47500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>57300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>37200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>136200</v>
+        <v>200600</v>
       </c>
       <c r="E21" s="3">
-        <v>252200</v>
+        <v>99500</v>
       </c>
       <c r="F21" s="3">
-        <v>-633200</v>
+        <v>186200</v>
       </c>
       <c r="G21" s="3">
-        <v>239400</v>
+        <v>389200</v>
       </c>
       <c r="H21" s="3">
-        <v>355700</v>
+        <v>177000</v>
       </c>
       <c r="I21" s="3">
-        <v>557600</v>
+        <v>259200</v>
       </c>
       <c r="J21" s="3">
+        <v>260100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1056400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>565900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>659500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>429300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>561700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>685500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>796500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>115800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>45200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>177500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>17300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K22" s="3">
+        <v>22500</v>
+      </c>
+      <c r="L22" s="3">
+        <v>24500</v>
+      </c>
+      <c r="M22" s="3">
         <v>21100</v>
       </c>
-      <c r="E22" s="3">
-        <v>18400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>22900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>20200</v>
-      </c>
-      <c r="H22" s="3">
-        <v>20200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>21900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>22500</v>
-      </c>
-      <c r="K22" s="3">
-        <v>24500</v>
-      </c>
-      <c r="L22" s="3">
-        <v>21100</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-46000</v>
+        <v>51500</v>
       </c>
       <c r="E23" s="3">
-        <v>55400</v>
+        <v>-33600</v>
       </c>
       <c r="F23" s="3">
-        <v>-915100</v>
+        <v>40900</v>
       </c>
       <c r="G23" s="3">
-        <v>68100</v>
+        <v>-693000</v>
       </c>
       <c r="H23" s="3">
-        <v>181100</v>
+        <v>50400</v>
       </c>
       <c r="I23" s="3">
-        <v>387600</v>
+        <v>136800</v>
       </c>
       <c r="J23" s="3">
+        <v>286400</v>
+      </c>
+      <c r="K23" s="3">
         <v>862000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>411200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>497600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>280200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>397200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-203500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>517000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>671300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-52200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-140000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-119000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>36400</v>
+        <v>13300</v>
       </c>
       <c r="E24" s="3">
-        <v>53100</v>
+        <v>26600</v>
       </c>
       <c r="F24" s="3">
-        <v>-112000</v>
+        <v>39200</v>
       </c>
       <c r="G24" s="3">
-        <v>10800</v>
+        <v>-84800</v>
       </c>
       <c r="H24" s="3">
-        <v>53200</v>
+        <v>8000</v>
       </c>
       <c r="I24" s="3">
-        <v>7200</v>
+        <v>40200</v>
       </c>
       <c r="J24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K24" s="3">
         <v>466600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>140100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>135000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>52600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-56400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>171300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-70000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-47700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-247700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-82400</v>
+        <v>38300</v>
       </c>
       <c r="E26" s="3">
-        <v>2300</v>
+        <v>-60200</v>
       </c>
       <c r="F26" s="3">
-        <v>-803100</v>
+        <v>1700</v>
       </c>
       <c r="G26" s="3">
-        <v>57300</v>
+        <v>-608100</v>
       </c>
       <c r="H26" s="3">
-        <v>127900</v>
+        <v>42400</v>
       </c>
       <c r="I26" s="3">
-        <v>380300</v>
+        <v>96600</v>
       </c>
       <c r="J26" s="3">
+        <v>281100</v>
+      </c>
+      <c r="K26" s="3">
         <v>395400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>271100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>362600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>284000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>344600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-147100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>451300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-57700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-69900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-71300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-82400</v>
+        <v>38300</v>
       </c>
       <c r="E27" s="3">
-        <v>2300</v>
+        <v>-60200</v>
       </c>
       <c r="F27" s="3">
-        <v>-803100</v>
+        <v>1700</v>
       </c>
       <c r="G27" s="3">
-        <v>57300</v>
+        <v>-608100</v>
       </c>
       <c r="H27" s="3">
-        <v>127900</v>
+        <v>42400</v>
       </c>
       <c r="I27" s="3">
-        <v>380300</v>
+        <v>96600</v>
       </c>
       <c r="J27" s="3">
+        <v>281100</v>
+      </c>
+      <c r="K27" s="3">
         <v>395400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>271100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>362600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>284000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>344600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-147100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>451300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-57700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-69900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-71300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>74500</v>
+        <v>-9200</v>
       </c>
       <c r="E32" s="3">
-        <v>-12100</v>
+        <v>3300</v>
       </c>
       <c r="F32" s="3">
-        <v>-93600</v>
+        <v>-14600</v>
       </c>
       <c r="G32" s="3">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="H32" s="3">
-        <v>-117700</v>
+        <v>-15100</v>
       </c>
       <c r="I32" s="3">
-        <v>140100</v>
+        <v>31900</v>
       </c>
       <c r="J32" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-477200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>141200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-53700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>324100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>376900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>139300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>51300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>14200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>22300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-47500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-57300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-37200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-82400</v>
+        <v>38300</v>
       </c>
       <c r="E33" s="3">
-        <v>2300</v>
+        <v>-60200</v>
       </c>
       <c r="F33" s="3">
-        <v>-803100</v>
+        <v>1700</v>
       </c>
       <c r="G33" s="3">
-        <v>57300</v>
+        <v>-608100</v>
       </c>
       <c r="H33" s="3">
-        <v>127900</v>
+        <v>42400</v>
       </c>
       <c r="I33" s="3">
-        <v>380300</v>
+        <v>96600</v>
       </c>
       <c r="J33" s="3">
+        <v>281100</v>
+      </c>
+      <c r="K33" s="3">
         <v>395400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>271100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>362600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>284000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>344600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-147100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>451300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-57700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-69900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-71300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-82400</v>
+        <v>38300</v>
       </c>
       <c r="E35" s="3">
-        <v>2300</v>
+        <v>-60200</v>
       </c>
       <c r="F35" s="3">
-        <v>-803100</v>
+        <v>1700</v>
       </c>
       <c r="G35" s="3">
-        <v>57300</v>
+        <v>-608100</v>
       </c>
       <c r="H35" s="3">
-        <v>127900</v>
+        <v>42400</v>
       </c>
       <c r="I35" s="3">
-        <v>380300</v>
+        <v>96600</v>
       </c>
       <c r="J35" s="3">
+        <v>281100</v>
+      </c>
+      <c r="K35" s="3">
         <v>395400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>271100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>362600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>284000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>344600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-147100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>451300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-57700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-69900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-71300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,96 +2657,100 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>264000</v>
+        <v>141300</v>
       </c>
       <c r="E41" s="3">
-        <v>254700</v>
+        <v>195600</v>
       </c>
       <c r="F41" s="3">
-        <v>140800</v>
+        <v>188100</v>
       </c>
       <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>50600</v>
+        <v>107100</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I41" s="3">
-        <v>99700</v>
+        <v>38300</v>
       </c>
       <c r="J41" s="3">
+        <v>73800</v>
+      </c>
+      <c r="K41" s="3">
         <v>13800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6000</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
       <c r="P41" s="3">
         <v>0</v>
       </c>
       <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>29000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>700</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>100</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -2677,8 +2767,8 @@
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2701,300 +2791,315 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>258500</v>
+        <v>203100</v>
       </c>
       <c r="E43" s="3">
-        <v>365200</v>
+        <v>188900</v>
       </c>
       <c r="F43" s="3">
-        <v>242900</v>
+        <v>269700</v>
       </c>
       <c r="G43" s="3">
-        <v>301700</v>
+        <v>183900</v>
       </c>
       <c r="H43" s="3">
-        <v>287900</v>
+        <v>223000</v>
       </c>
       <c r="I43" s="3">
-        <v>334600</v>
+        <v>217400</v>
       </c>
       <c r="J43" s="3">
+        <v>247300</v>
+      </c>
+      <c r="K43" s="3">
         <v>373700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>391200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>369400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>396700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>328600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>281600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>205900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>240500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>196100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>179400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>233000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>188400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>211400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>45400</v>
+        <v>21600</v>
       </c>
       <c r="E44" s="3">
-        <v>32400</v>
+        <v>33200</v>
       </c>
       <c r="F44" s="3">
-        <v>57300</v>
+        <v>23900</v>
       </c>
       <c r="G44" s="3">
-        <v>26900</v>
+        <v>43400</v>
       </c>
       <c r="H44" s="3">
-        <v>21300</v>
+        <v>19900</v>
       </c>
       <c r="I44" s="3">
-        <v>30700</v>
+        <v>16100</v>
       </c>
       <c r="J44" s="3">
+        <v>22700</v>
+      </c>
+      <c r="K44" s="3">
         <v>19700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>30800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>25800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>20100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>24600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>17100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>21500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>15800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>29400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>169400</v>
+        <v>68500</v>
       </c>
       <c r="E45" s="3">
-        <v>234200</v>
+        <v>71000</v>
       </c>
       <c r="F45" s="3">
-        <v>381800</v>
+        <v>118300</v>
       </c>
       <c r="G45" s="3">
-        <v>328600</v>
+        <v>237600</v>
       </c>
       <c r="H45" s="3">
-        <v>383600</v>
+        <v>195900</v>
       </c>
       <c r="I45" s="3">
-        <v>388800</v>
+        <v>246300</v>
       </c>
       <c r="J45" s="3">
+        <v>249300</v>
+      </c>
+      <c r="K45" s="3">
         <v>307300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>168700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>134200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>126800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>118200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>155800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>44600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>65800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>83100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>123900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>77900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>740900</v>
+        <v>482000</v>
       </c>
       <c r="E46" s="3">
-        <v>886400</v>
+        <v>541300</v>
       </c>
       <c r="F46" s="3">
-        <v>823500</v>
+        <v>654600</v>
       </c>
       <c r="G46" s="3">
-        <v>657300</v>
+        <v>623600</v>
       </c>
       <c r="H46" s="3">
-        <v>743500</v>
+        <v>485900</v>
       </c>
       <c r="I46" s="3">
-        <v>854000</v>
+        <v>561500</v>
       </c>
       <c r="J46" s="3">
+        <v>631200</v>
+      </c>
+      <c r="K46" s="3">
         <v>714400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>598500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>530100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>551900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>472800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>460100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>292800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>300000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>261000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>267600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>342400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>344700</v>
-      </c>
-      <c r="V46" s="3">
-        <v>347700</v>
       </c>
       <c r="W46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>80100</v>
+        <v>58700</v>
       </c>
       <c r="E47" s="3">
-        <v>80300</v>
+        <v>58500</v>
       </c>
       <c r="F47" s="3">
-        <v>73300</v>
+        <v>59300</v>
       </c>
       <c r="G47" s="3">
-        <v>68300</v>
+        <v>55500</v>
       </c>
       <c r="H47" s="3">
-        <v>58600</v>
+        <v>50500</v>
       </c>
       <c r="I47" s="3">
-        <v>52100</v>
+        <v>44300</v>
       </c>
       <c r="J47" s="3">
+        <v>38500</v>
+      </c>
+      <c r="K47" s="3">
         <v>56400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>47800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>38100</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -3011,8 +3116,8 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3026,73 +3131,79 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5188400</v>
+        <v>3848300</v>
       </c>
       <c r="E48" s="3">
-        <v>5140400</v>
+        <v>3790900</v>
       </c>
       <c r="F48" s="3">
-        <v>5080900</v>
+        <v>3796200</v>
       </c>
       <c r="G48" s="3">
-        <v>6282900</v>
+        <v>3847300</v>
       </c>
       <c r="H48" s="3">
-        <v>6235400</v>
+        <v>4644500</v>
       </c>
       <c r="I48" s="3">
-        <v>6226800</v>
+        <v>4708800</v>
       </c>
       <c r="J48" s="3">
+        <v>4602200</v>
+      </c>
+      <c r="K48" s="3">
         <v>5962100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5646000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5421300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5175200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5057500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4915500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4816300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4071700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3361200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3352000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3553000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3531500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5301800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>173400</v>
+        <v>20100</v>
       </c>
       <c r="E52" s="3">
-        <v>217500</v>
+        <v>24800</v>
       </c>
       <c r="F52" s="3">
-        <v>258200</v>
+        <v>44300</v>
       </c>
       <c r="G52" s="3">
-        <v>152700</v>
+        <v>57600</v>
       </c>
       <c r="H52" s="3">
-        <v>142400</v>
+        <v>12500</v>
       </c>
       <c r="I52" s="3">
-        <v>152200</v>
+        <v>10300</v>
       </c>
       <c r="J52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K52" s="3">
         <v>258100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>316300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>292100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>472000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>375000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>374000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>298400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>354800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>486900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>506800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>466700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>496200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>216700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6182800</v>
+        <v>4503600</v>
       </c>
       <c r="E54" s="3">
-        <v>6324600</v>
+        <v>4517500</v>
       </c>
       <c r="F54" s="3">
-        <v>6235800</v>
+        <v>4670600</v>
       </c>
       <c r="G54" s="3">
-        <v>7161200</v>
+        <v>4721900</v>
       </c>
       <c r="H54" s="3">
-        <v>7180000</v>
+        <v>5293800</v>
       </c>
       <c r="I54" s="3">
-        <v>7285200</v>
+        <v>5422100</v>
       </c>
       <c r="J54" s="3">
+        <v>5384400</v>
+      </c>
+      <c r="K54" s="3">
         <v>6991100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6608600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6281600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6199100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5905300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5749600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5407500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4726500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4109100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4126400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4362100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4372300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5866100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,87 +3661,91 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>361200</v>
+        <v>237600</v>
       </c>
       <c r="E57" s="3">
-        <v>406300</v>
+        <v>243300</v>
       </c>
       <c r="F57" s="3">
-        <v>380400</v>
+        <v>284900</v>
       </c>
       <c r="G57" s="3">
-        <v>368700</v>
+        <v>272100</v>
       </c>
       <c r="H57" s="3">
-        <v>428500</v>
+        <v>272500</v>
       </c>
       <c r="I57" s="3">
-        <v>469900</v>
+        <v>323600</v>
       </c>
       <c r="J57" s="3">
+        <v>347300</v>
+      </c>
+      <c r="K57" s="3">
         <v>481400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>444700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>422800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>398900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>440700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>364500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>346500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>312000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>297700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>246700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>309600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>441800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>312400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>20600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3661,268 +3795,283 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>318300</v>
+        <v>131100</v>
       </c>
       <c r="E59" s="3">
-        <v>360900</v>
+        <v>232600</v>
       </c>
       <c r="F59" s="3">
-        <v>315700</v>
+        <v>266500</v>
       </c>
       <c r="G59" s="3">
-        <v>364800</v>
+        <v>239100</v>
       </c>
       <c r="H59" s="3">
-        <v>442200</v>
+        <v>269600</v>
       </c>
       <c r="I59" s="3">
-        <v>564500</v>
+        <v>334000</v>
       </c>
       <c r="J59" s="3">
+        <v>417200</v>
+      </c>
+      <c r="K59" s="3">
         <v>410600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>542300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>535800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>655900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>306200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>531500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>181700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>73300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>135500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>84200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>58800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>64500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>103800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>679500</v>
+        <v>386100</v>
       </c>
       <c r="E60" s="3">
-        <v>767200</v>
+        <v>496500</v>
       </c>
       <c r="F60" s="3">
-        <v>696100</v>
+        <v>566600</v>
       </c>
       <c r="G60" s="3">
-        <v>733400</v>
+        <v>527100</v>
       </c>
       <c r="H60" s="3">
-        <v>870800</v>
+        <v>542200</v>
       </c>
       <c r="I60" s="3">
-        <v>1034400</v>
+        <v>657600</v>
       </c>
       <c r="J60" s="3">
+        <v>764500</v>
+      </c>
+      <c r="K60" s="3">
         <v>892000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>987100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>958700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1054900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>746800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>896000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>528200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>385300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>433100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>330900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>368400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>506300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>416200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1008600</v>
+        <v>758800</v>
       </c>
       <c r="E61" s="3">
-        <v>962400</v>
+        <v>736900</v>
       </c>
       <c r="F61" s="3">
-        <v>947000</v>
+        <v>710700</v>
       </c>
       <c r="G61" s="3">
-        <v>1003300</v>
+        <v>717100</v>
       </c>
       <c r="H61" s="3">
-        <v>954700</v>
+        <v>741700</v>
       </c>
       <c r="I61" s="3">
-        <v>979900</v>
+        <v>721000</v>
       </c>
       <c r="J61" s="3">
+        <v>724200</v>
+      </c>
+      <c r="K61" s="3">
         <v>1132900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1463400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1579300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1436100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1711800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1827400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1841500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1984200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2010400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2153200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2220700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2085300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2017700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1664100</v>
+        <v>946800</v>
       </c>
       <c r="E62" s="3">
-        <v>1612800</v>
+        <v>940300</v>
       </c>
       <c r="F62" s="3">
-        <v>1561100</v>
+        <v>916400</v>
       </c>
       <c r="G62" s="3">
-        <v>1572100</v>
+        <v>893600</v>
       </c>
       <c r="H62" s="3">
-        <v>1531500</v>
+        <v>838800</v>
       </c>
       <c r="I62" s="3">
-        <v>1491300</v>
+        <v>797300</v>
       </c>
       <c r="J62" s="3">
+        <v>743100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1565100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1268100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1062100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1379600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1380600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1290800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1176000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>946500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>740200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>663200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>742300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>628400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>978900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3352200</v>
+        <v>2372800</v>
       </c>
       <c r="E66" s="3">
-        <v>3342400</v>
+        <v>2449300</v>
       </c>
       <c r="F66" s="3">
-        <v>3204200</v>
+        <v>2468300</v>
       </c>
       <c r="G66" s="3">
-        <v>3308800</v>
+        <v>2426200</v>
       </c>
       <c r="H66" s="3">
-        <v>3357000</v>
+        <v>2446000</v>
       </c>
       <c r="I66" s="3">
-        <v>3505500</v>
+        <v>2535100</v>
       </c>
       <c r="J66" s="3">
+        <v>2590900</v>
+      </c>
+      <c r="K66" s="3">
         <v>3590000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3718600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3600100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3870600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3839200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4014300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3545700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3315900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3183700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3147300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3331400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3220000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3412800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1332500</v>
+        <v>-937800</v>
       </c>
       <c r="E72" s="3">
-        <v>-1254600</v>
+        <v>-973600</v>
       </c>
       <c r="F72" s="3">
-        <v>-1263600</v>
+        <v>-926500</v>
       </c>
       <c r="G72" s="3">
-        <v>-458100</v>
+        <v>-956800</v>
       </c>
       <c r="H72" s="3">
-        <v>-503500</v>
+        <v>-338600</v>
       </c>
       <c r="I72" s="3">
-        <v>-626700</v>
+        <v>-380200</v>
       </c>
       <c r="J72" s="3">
+        <v>-463200</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2830600</v>
+        <v>2130800</v>
       </c>
       <c r="E76" s="3">
-        <v>2982200</v>
+        <v>2068200</v>
       </c>
       <c r="F76" s="3">
-        <v>3031600</v>
+        <v>2202300</v>
       </c>
       <c r="G76" s="3">
-        <v>3852400</v>
+        <v>2295600</v>
       </c>
       <c r="H76" s="3">
-        <v>3823000</v>
+        <v>2847800</v>
       </c>
       <c r="I76" s="3">
-        <v>3779700</v>
+        <v>2887100</v>
       </c>
       <c r="J76" s="3">
+        <v>2793500</v>
+      </c>
+      <c r="K76" s="3">
         <v>3401100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2889900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2681500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2328500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2066100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1735400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1861800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1410600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>925400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>979100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1030700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1152300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2453300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-82400</v>
+        <v>38300</v>
       </c>
       <c r="E81" s="3">
-        <v>2300</v>
+        <v>-60200</v>
       </c>
       <c r="F81" s="3">
-        <v>-803100</v>
+        <v>1700</v>
       </c>
       <c r="G81" s="3">
-        <v>57300</v>
+        <v>-608100</v>
       </c>
       <c r="H81" s="3">
-        <v>127900</v>
+        <v>42400</v>
       </c>
       <c r="I81" s="3">
-        <v>380300</v>
+        <v>96600</v>
       </c>
       <c r="J81" s="3">
+        <v>281100</v>
+      </c>
+      <c r="K81" s="3">
         <v>395400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>271100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>362600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>284000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>344600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-147100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>451300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-57700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-69900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-71300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>161200</v>
+        <v>111700</v>
       </c>
       <c r="E83" s="3">
-        <v>178400</v>
+        <v>116600</v>
       </c>
       <c r="F83" s="3">
-        <v>259000</v>
+        <v>109500</v>
       </c>
       <c r="G83" s="3">
-        <v>151100</v>
+        <v>127000</v>
       </c>
       <c r="H83" s="3">
-        <v>154400</v>
+        <v>94800</v>
       </c>
       <c r="I83" s="3">
-        <v>148100</v>
+        <v>109300</v>
       </c>
       <c r="J83" s="3">
+        <v>107500</v>
+      </c>
+      <c r="K83" s="3">
         <v>171900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>130200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>140800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>134200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>148200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>167800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>149700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>106000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>148200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>167700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>106700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>157800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>139900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>266300</v>
+        <v>99600</v>
       </c>
       <c r="E89" s="3">
-        <v>354300</v>
+        <v>194600</v>
       </c>
       <c r="F89" s="3">
-        <v>343800</v>
+        <v>261600</v>
       </c>
       <c r="G89" s="3">
-        <v>118400</v>
+        <v>260400</v>
       </c>
       <c r="H89" s="3">
-        <v>173600</v>
+        <v>87600</v>
       </c>
       <c r="I89" s="3">
-        <v>388600</v>
+        <v>131100</v>
       </c>
       <c r="J89" s="3">
+        <v>287200</v>
+      </c>
+      <c r="K89" s="3">
         <v>495200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>447600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>530400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>341100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>250400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>211500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>253400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>119100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>135100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>93800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>278400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>220500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-116100</v>
+        <v>-91000</v>
       </c>
       <c r="E91" s="3">
-        <v>-190800</v>
+        <v>-84800</v>
       </c>
       <c r="F91" s="3">
-        <v>-145600</v>
+        <v>-140900</v>
       </c>
       <c r="G91" s="3">
-        <v>-128800</v>
+        <v>-110200</v>
       </c>
       <c r="H91" s="3">
-        <v>-169000</v>
+        <v>-95200</v>
       </c>
       <c r="I91" s="3">
-        <v>-289000</v>
+        <v>-127700</v>
       </c>
       <c r="J91" s="3">
+        <v>-213600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-172900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-186200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-611000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-92100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-172700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-158600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-153000</v>
+        <v>-107900</v>
       </c>
       <c r="E94" s="3">
-        <v>-181300</v>
+        <v>-111800</v>
       </c>
       <c r="F94" s="3">
-        <v>-132900</v>
+        <v>-133900</v>
       </c>
       <c r="G94" s="3">
-        <v>-170400</v>
+        <v>-100700</v>
       </c>
       <c r="H94" s="3">
-        <v>-164400</v>
+        <v>-126000</v>
       </c>
       <c r="I94" s="3">
-        <v>-108700</v>
+        <v>-124200</v>
       </c>
       <c r="J94" s="3">
+        <v>-80300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-168100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-168300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-612600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-110300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-134900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-162900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-97200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-74700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-50600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-41800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-122000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-187000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-117000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,38 +6014,39 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-19200</v>
+        <v>14100</v>
       </c>
       <c r="E96" s="3">
-        <v>-16200</v>
+        <v>14000</v>
       </c>
       <c r="F96" s="3">
-        <v>-16400</v>
+        <v>12000</v>
       </c>
       <c r="G96" s="3">
-        <v>-16400</v>
+        <v>12400</v>
       </c>
       <c r="H96" s="3">
-        <v>-16200</v>
+        <v>12100</v>
       </c>
       <c r="I96" s="3">
-        <v>-13100</v>
+        <v>12300</v>
       </c>
       <c r="J96" s="3">
+        <v>9700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-13000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-10000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -5835,19 +6069,22 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-17400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-100300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-97300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-99500</v>
+        <v>-48700</v>
       </c>
       <c r="E100" s="3">
-        <v>-60700</v>
+        <v>-72700</v>
       </c>
       <c r="F100" s="3">
-        <v>-81700</v>
+        <v>-44800</v>
       </c>
       <c r="G100" s="3">
-        <v>700</v>
+        <v>-61800</v>
       </c>
       <c r="H100" s="3">
-        <v>-45200</v>
+        <v>500</v>
       </c>
       <c r="I100" s="3">
-        <v>-194200</v>
+        <v>-34100</v>
       </c>
       <c r="J100" s="3">
+        <v>-143500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-323000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-272500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>78500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-231400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-108000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-48400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-159900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-47200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-83200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-51200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>118200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-104400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-85200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="F101" s="3">
+        <v>200</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>12200</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L101" s="3">
+        <v>300</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>100</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="S101" s="3">
+        <v>300</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="V101" s="3">
+        <v>600</v>
+      </c>
+      <c r="W101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
-        <v>-13200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R101" s="3">
-        <v>300</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
-        <v>500</v>
-      </c>
-      <c r="W101" s="3">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>13000</v>
+        <v>-56800</v>
       </c>
       <c r="E102" s="3">
-        <v>113200</v>
+        <v>9500</v>
       </c>
       <c r="F102" s="3">
-        <v>141500</v>
+        <v>83600</v>
       </c>
       <c r="G102" s="3">
-        <v>-50700</v>
+        <v>107100</v>
       </c>
       <c r="H102" s="3">
-        <v>-49100</v>
+        <v>-37500</v>
       </c>
       <c r="I102" s="3">
-        <v>86000</v>
+        <v>-37100</v>
       </c>
       <c r="J102" s="3">
+        <v>63600</v>
+      </c>
+      <c r="K102" s="3">
         <v>6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6000</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,314 +656,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>322700</v>
+      </c>
+      <c r="E8" s="3">
         <v>331100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>315900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>339300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>361800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>327700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>320500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>358700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>824600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>965300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>838700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>786600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>745100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>524600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>395600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>375500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>320000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>274800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>192800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>353300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>423100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>113700</v>
+      </c>
+      <c r="E9" s="3">
         <v>122500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>121000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>127200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>105500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>106700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>119800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>118200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>186500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>209400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>178000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>159900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>150600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>139900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>129600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>140000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>138500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>114100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>115300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>177200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>185500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E10" s="3">
         <v>208600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>194900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>212100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>256300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>221000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>240600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>638100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>755900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>660700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>626700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>594500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>384700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>266000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>235500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>181500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>160700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>77500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>176100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>237600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1069,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1138,21 +1157,21 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>99300</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-9500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-152000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1160,108 +1179,114 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-192100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-23900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-610800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-662900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>47800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>69700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1564900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>46100</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>113600</v>
+      </c>
+      <c r="E15" s="3">
         <v>133400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>117800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>131800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>965500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>111700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>116600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>109500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>171900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>130200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>140800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>134200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>148200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>167800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>149700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>106000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>148200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>167700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>106700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>157800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>139900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>340300</v>
+      </c>
+      <c r="E17" s="3">
         <v>254800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>337400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>270300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>940300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>247300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>209800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>195400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>417300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>388500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>373700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>167400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>319000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>332500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-279500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-366300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>338200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>375000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>341400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1956800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>422700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E18" s="3">
         <v>76400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-21500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>69000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-578500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>80500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>110600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>163300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>407300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>576800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>465000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>619200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>426100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>192100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>675100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>741800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-18200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-148600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,348 +1477,364 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E20" s="3">
         <v>9200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>14600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>15100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-31900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>12700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>477200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-141200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>53700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-324100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-376900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-139300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-51300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-14200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-22300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>47500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>57300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>37200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E21" s="3">
         <v>200600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>99500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>186200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>389200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>177000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>259200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>260100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1056400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>565900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>659500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>429300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>561700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>685500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>796500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>115800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>45200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>177500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E22" s="3">
         <v>15700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="E23" s="3">
         <v>51500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-693000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>136800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>286400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>862000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>411200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>497600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>280200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>397200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-203500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>517000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>671300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-52200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-140000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-119000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E24" s="3">
         <v>13300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-84800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>40200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>466600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>140100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>135000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>52600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-56400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>65700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>171300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-70000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-47700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-247700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>17000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E26" s="3">
         <v>38300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-60200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-608100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>42400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>96600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>281100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>395400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>271100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>362600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>284000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>344600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>451300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>500000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-57700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-69900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-71300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>38300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-60200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-608100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>42400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>96600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>281100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>395400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>271100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>362600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>284000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>344600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>451300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-57700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-69900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-71300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2327,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-14600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-15100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>31900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-12700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-477200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>141200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-53700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>324100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>376900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>139300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>51300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>14200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>22300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-47500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-57300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-37200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>38300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-60200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-608100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>42400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>96600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>281100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>395400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>271100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>362600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>284000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>344600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>451300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-57700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-69900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-71300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>38300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-60200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-608100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>42400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>96600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>281100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>395400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>271100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>362600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>284000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>344600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>451300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-57700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-69900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-71300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2743,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E41" s="3">
         <v>141300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>195600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>188100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>107100</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="I41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6000</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
         <v>0</v>
       </c>
       <c r="R41" s="3">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3">
         <v>3600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>29000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2752,8 +2841,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
@@ -2770,8 +2859,8 @@
       <c r="P42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2794,315 +2883,330 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>207500</v>
+      </c>
+      <c r="E43" s="3">
         <v>203100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>188900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>269700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>183900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>223000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>217400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>247300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>373700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>391200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>369400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>396700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>328600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>281600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>205900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>240500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>196100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>179400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>233000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>188400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>211400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E44" s="3">
         <v>21600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>33200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>23900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>43400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>19900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>22700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>30800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>25800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>20100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>22800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>28500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>24600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>17100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>21500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>15800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>29400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E45" s="3">
         <v>68500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>71000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>118300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>237600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>195900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>246300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>249300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>307300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>168700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>134200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>126800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>118200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>155800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>44600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>65800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>83100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>123900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>77900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E46" s="3">
         <v>482000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>541300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>654600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>623600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>485900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>561500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>631200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>714400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>598500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>530100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>551900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>472800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>460100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>292800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>300000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>261000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>267600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>342400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>344700</v>
-      </c>
-      <c r="W46" s="3">
-        <v>347700</v>
       </c>
       <c r="X46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E47" s="3">
         <v>58700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>58500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>55500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>50500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>44300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>38500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>56400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>47800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>38100</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -3119,8 +3223,8 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3134,76 +3238,82 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3643700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3848300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3790900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3796200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3847300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4644500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4708800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4602200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5962100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5646000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5421300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5175200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5057500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4915500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4816300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4071700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3361200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3352000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3553000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3531500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5301800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3522,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E52" s="3">
         <v>20100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>57600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>258100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>316300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>292100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>472000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>375000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>374000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>298400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>354800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>486900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>506800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>466700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>496200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>216700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3664,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4250400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4503600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4517500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4670600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4721900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5293800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5422100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5384400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6991100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6608600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6281600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6199100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5905300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5749600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5407500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4726500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4109100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4126400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4362100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4372300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5866100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,94 +3791,98 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>287200</v>
+      </c>
+      <c r="E57" s="3">
         <v>237600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>243300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>284900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>272100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>272500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>323600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>347300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>481400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>444700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>422800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>398900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>440700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>364500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>346500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>312000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>297700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>246700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>309600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>441800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>312400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E58" s="3">
         <v>17400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3798,280 +3931,295 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>128700</v>
+      </c>
+      <c r="E59" s="3">
         <v>131100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>232600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>266500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>239100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>269600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>334000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>417200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>410600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>542300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>535800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>655900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>306200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>531500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>181700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>73300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>135500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>84200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>58800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>64500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>103800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>424400</v>
+      </c>
+      <c r="E60" s="3">
         <v>386100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>496500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>566600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>527100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>542200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>657600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>764500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>892000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>987100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>958700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1054900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>746800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>896000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>528200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>385300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>433100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>330900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>368400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>506300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>416200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>707800</v>
+      </c>
+      <c r="E61" s="3">
         <v>758800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>736900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>710700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>717100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>741700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>721000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>724200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1132900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1463400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1579300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1436100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1711800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1827400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1841500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1984200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2010400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2153200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2220700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2085300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2017700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>911000</v>
+      </c>
+      <c r="E62" s="3">
         <v>946800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>940300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>916400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>893600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>838800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>797300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>743100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1565100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1268100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1062100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1379600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1380600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1290800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1176000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>946500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>740200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>663200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>742300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>628400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>978900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4428,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2296700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2372800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2449300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2468300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2426200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2446000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2535100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2590900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3590000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3718600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3600100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3870600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3839200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4014300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3545700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3315900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3183700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3147300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3331400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3220000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3412800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4810,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-895800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-937800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-973600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-926500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-956800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-338600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-380200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-463200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5094,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1953600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2130800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2068200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2202300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2295600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2847800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2887100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2793500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3401100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2889900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2681500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2328500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2066100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1735400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1861800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1410600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>925400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>979100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1030700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1152300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2453300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>38300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-60200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-608100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>42400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>96600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>281100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>395400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>271100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>362600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>284000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>344600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-147100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>451300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-57700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-69900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-71300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5412,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E83" s="3">
         <v>111700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>116600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>109500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>127000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>94800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>109300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>107500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>171900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>140800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>134200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>148200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>167800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>149700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>106000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>148200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>167700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>106700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>157800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>139900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E89" s="3">
         <v>99600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>194600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>261600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>260400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>87600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>131100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>287200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>495200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>447600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>530400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>341100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>250400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>211500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>253400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>119100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>135100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>93800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>278400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>220500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-143100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-91000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-84800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-140900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-110200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-95200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-127700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-213600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-172900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-186200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-611000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-92100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-172700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-158600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-107500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-107900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-111800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-133900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-126000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-124200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-80300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-168100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-168300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-612600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-110300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-134900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-162900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-97200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-74700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-50600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-41800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-122000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-187000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-117000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,41 +6247,42 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E96" s="3">
         <v>14100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>14000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>12000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>12400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>12100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>12300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>9700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-13000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-10000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -6072,19 +6305,22 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-17400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-100300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-97300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,208 +6529,220 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-82000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-48700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-72700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-61800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-34100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-143500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-323000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-272500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>78500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-231400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-108000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-48400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-159900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-47200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-83200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-51200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>118200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-104400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-85200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-56800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>107100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-37100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>63600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6000</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,326 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>361500</v>
+      </c>
+      <c r="E8" s="3">
         <v>322700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>331100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>315900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>339300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>361800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>327700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>320500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>358700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>824600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>965300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>838700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>786600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>745100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>524600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>395600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>375500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>320000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>274800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>192800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>353300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>423100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E9" s="3">
         <v>113700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>122500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>121000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>127200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>105500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>106700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>119800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>186500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>209400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>178000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>159900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>150600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>139900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>129600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>140000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>138500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>114100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>115300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>177200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>185500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>241100</v>
+      </c>
+      <c r="E10" s="3">
         <v>209000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>208600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>194900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>212100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>256300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>221000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>240600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>638100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>755900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>660700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>626700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>594500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>384700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>266000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>235500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>181500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>160700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>77500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>176100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>237600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1001,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1072,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,8 +1160,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1160,21 +1180,21 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>99300</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-9500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-152000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1182,111 +1202,117 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-192100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-22200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-610800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-662900</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>47800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>69700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1564900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>46100</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E15" s="3">
         <v>113600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>133400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>117800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>131800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>965500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>111700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>116600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>171900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>130200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>140800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>134200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>148200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>167800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>149700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>106000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>148200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>167700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>106700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>157800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>139900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>285500</v>
+      </c>
+      <c r="E17" s="3">
         <v>340300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>254800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>337400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>270300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>940300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>247300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>209800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>195400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>417300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>388500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>373700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>167400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>319000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>332500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-279500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-366300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>338200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>375000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>341400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1956800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>422700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>76400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-21500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>69000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-578500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>80500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>110600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>163300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>407300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>576800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>465000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>619200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>426100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>192100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>675100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>741800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-148600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,363 +1511,379 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E20" s="3">
         <v>25200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>15100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-31900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>477200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-141200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>53700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-324100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-376900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-139300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-51300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-14200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-22300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>47500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>57300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>37200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>165200</v>
+      </c>
+      <c r="E21" s="3">
         <v>70800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>99500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>186200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>389200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>177000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>259200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>260100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1056400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>565900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>659500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>429300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>561700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>685500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>796500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>115800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>45200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>177500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E22" s="3">
         <v>16700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-59500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>40900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-693000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>136800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>286400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>862000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>411200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>497600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>280200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>397200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-203500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>517000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>671300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-52200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-140000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-119000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>18400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-46700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-84800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>466600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>140100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>135000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>52600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-56400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>65700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>171300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-70000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-47700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-247700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>17000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>38300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-60200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-608100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>42400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>96600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>281100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>395400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>271100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>362600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>284000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>344600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-147100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>451300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-57700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-69900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-71300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>38300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-60200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-608100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>42400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>96600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>281100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>395400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>271100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>362600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>284000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>344600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-147100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>451300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-57700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-69900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-71300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-33500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-25200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-15100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>31900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-477200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>141200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-53700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>324100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>376900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>139300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>51300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>14200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>22300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-47500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-57300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>38300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-60200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-608100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>42400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>96600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>281100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>395400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>271100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>362600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>284000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>344600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-147100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>451300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-57700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-69900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-71300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>38300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-60200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-608100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>42400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>96600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>281100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>395400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>271100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>362600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>284000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>344600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-147100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>451300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-57700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-69900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-71300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E41" s="3">
         <v>91600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>141300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>195600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>188100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>107100</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>73800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6000</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
       <c r="R41" s="3">
         <v>0</v>
       </c>
       <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
         <v>3600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2844,8 +2934,8 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
@@ -2862,8 +2952,8 @@
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2886,150 +2976,159 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E43" s="3">
         <v>207500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>203100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>188900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>269700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>183900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>223000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>217400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>247300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>373700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>391200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>369400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>396700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>328600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>281600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>205900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>240500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>196100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>179400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>233000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>188400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>211400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E44" s="3">
         <v>28300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>21600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>33200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>43400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>19900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>22700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>30800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>25800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>20100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>22800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>28500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>24600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>21500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>15800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>29400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3037,179 +3136,185 @@
         <v>28000</v>
       </c>
       <c r="E45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F45" s="3">
         <v>68500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>71000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>118300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>237600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>195900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>246300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>249300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>307300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>168700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>134200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>126800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>118200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>155800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>58300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>31300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>44600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>65800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>83100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>123900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>77900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>354600</v>
+      </c>
+      <c r="E46" s="3">
         <v>404700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>482000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>541300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>654600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>623600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>485900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>561500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>631200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>714400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>598500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>530100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>551900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>472800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>460100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>292800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>300000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>261000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>267600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>342400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>344700</v>
-      </c>
-      <c r="X46" s="3">
-        <v>347700</v>
       </c>
       <c r="Y46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E47" s="3">
         <v>54800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>58700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>58500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>55500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>50500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>44300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>38500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>56400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38100</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -3226,8 +3331,8 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3241,79 +3346,85 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4470600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3643700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3848300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3790900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3796200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3847300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4644500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4708800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4602200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5962100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5646000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5421300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5175200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5057500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4915500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4816300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4071700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3361200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3352000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3553000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3531500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5301800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,79 +3642,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E52" s="3">
         <v>9700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>44300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>258100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>316300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>292100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>472000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>375000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>374000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>298400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>354800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>486900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>506800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>466700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>496200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>216700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4928400</v>
+      </c>
+      <c r="E54" s="3">
         <v>4250400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4503600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4517500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4670600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4721900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5293800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5422100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5384400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6991100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6608600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6281600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6199100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5905300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5749600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5407500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4726500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4109100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4126400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4362100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4372300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5866100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,100 +3922,104 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>369800</v>
+      </c>
+      <c r="E57" s="3">
         <v>287200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>237600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>243300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>284900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>272100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>272500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>323600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>347300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>481400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>444700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>422800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>398900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>440700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>364500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>346500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>312000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>297700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>246700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>309600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>441800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>312400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>17400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -3934,292 +4068,307 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E59" s="3">
         <v>128700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>131100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>232600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>266500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>239100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>269600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>334000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>417200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>410600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>542300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>535800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>655900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>306200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>531500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>181700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>73300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>135500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>84200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>58800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>64500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>103800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>499600</v>
+      </c>
+      <c r="E60" s="3">
         <v>424400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>386100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>496500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>566600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>527100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>542200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>657600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>764500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>892000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>987100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>958700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1054900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>746800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>896000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>528200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>385300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>433100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>330900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>368400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>506300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>416200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1343400</v>
+      </c>
+      <c r="E61" s="3">
         <v>707800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>758800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>736900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>710700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>717100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>741700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>721000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>724200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1132900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1463400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1579300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1436100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1711800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1827400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1841500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1984200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2010400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2153200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2220700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2085300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2017700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>816900</v>
+      </c>
+      <c r="E62" s="3">
         <v>911000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>946800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>940300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>916400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>893600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>838800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>797300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>743100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1565100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1268100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1062100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1379600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1380600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1290800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1176000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>946500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>740200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>663200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>742300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>628400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>978900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2923800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2296700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2372800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2449300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2468300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2426200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2446000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2535100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2590900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3590000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3718600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3600100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3870600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3839200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4014300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3545700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3315900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3183700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3147300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3331400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3220000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3412800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-889200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-895800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-937800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-973600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-926500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-956800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-338600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-380200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-463200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2004600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1953600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2130800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2068200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2202300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2295600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2847800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2887100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2793500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3401100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2889900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2681500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2328500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2066100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1735400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1861800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1410600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>925400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>979100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1030700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1152300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2453300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>38300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-60200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-608100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>42400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>96600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>281100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>395400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>271100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>362600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>284000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>344600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-147100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>451300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-57700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-69900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-71300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,79 +5611,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E83" s="3">
         <v>196100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>111700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>116600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>109500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>127000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>94800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>109300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>107500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>171900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>130200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>140800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>134200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>148200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>167800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>149700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>106000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>148200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>167700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>106700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>157800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>139900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>195100</v>
+      </c>
+      <c r="E89" s="3">
         <v>147700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>99600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>194600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>261600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>260400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>87600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>131100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>287200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>495200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>447600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>530400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>341100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>250400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>211500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>253400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>119100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>135100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>93800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>278400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>220500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-881200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-143100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-91000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-84800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-140900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-110200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-95200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-127700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-213600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-172900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-186200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-611000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-92100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-172700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-158600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-873700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-107500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-107900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-111800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-133900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-100700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-126000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-124200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-168100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-168300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-612600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-110300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-134900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-162900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-97200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-74700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-50600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-122000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-187000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-117000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,44 +6481,45 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E96" s="3">
         <v>13000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>14100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>14000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>12000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>12400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>12100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>12300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>9700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-13000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-10000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -6308,19 +6542,22 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-17400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-100300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-97300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>602500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-82000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-72700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-61800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-34100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-143500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-323000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-272500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>78500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-231400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-48400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-159900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-47200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-83200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-51200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>118200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-104400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-85200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>9300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-75300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-41200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-56800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>83600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>107100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-37500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-37100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>63600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>361500</v>
+        <v>304000</v>
       </c>
       <c r="E8" s="3">
+        <v>305100</v>
+      </c>
+      <c r="F8" s="3">
         <v>322700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>331100</v>
       </c>
-      <c r="G8" s="3">
-        <v>315900</v>
-      </c>
       <c r="H8" s="3">
-        <v>339300</v>
+        <v>241800</v>
       </c>
       <c r="I8" s="3">
+        <v>273200</v>
+      </c>
+      <c r="J8" s="3">
         <v>361800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>327700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>320500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>358700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>824600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>965300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>838700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>786600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>745100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>524600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>395600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>375500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>320000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>274800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>192800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>353300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>423100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>120300</v>
+        <v>114800</v>
       </c>
       <c r="E9" s="3">
+        <v>98900</v>
+      </c>
+      <c r="F9" s="3">
         <v>113700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>122500</v>
       </c>
-      <c r="G9" s="3">
-        <v>121000</v>
-      </c>
       <c r="H9" s="3">
-        <v>127200</v>
+        <v>97900</v>
       </c>
       <c r="I9" s="3">
+        <v>99000</v>
+      </c>
+      <c r="J9" s="3">
         <v>105500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>106700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>119800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>118200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>186500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>209400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>178000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>159900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>150600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>139900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>129600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>140000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>138500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>114100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>115300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>177200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>185500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>241100</v>
+        <v>189100</v>
       </c>
       <c r="E10" s="3">
+        <v>206300</v>
+      </c>
+      <c r="F10" s="3">
         <v>209000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>208600</v>
       </c>
-      <c r="G10" s="3">
-        <v>194900</v>
-      </c>
       <c r="H10" s="3">
-        <v>212100</v>
+        <v>143900</v>
       </c>
       <c r="I10" s="3">
+        <v>174100</v>
+      </c>
+      <c r="J10" s="3">
         <v>256300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>221000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>240600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>638100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>755900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>660700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>626700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>594500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>384700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>266000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>235500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>181500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>160700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>77500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>176100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>237600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1183,21 +1203,21 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>99300</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-9500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-152000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1205,114 +1225,120 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-192100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-23900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-22200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-610800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-662900</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>47800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>69700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1564900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>46100</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>122700</v>
+        <v>121500</v>
       </c>
       <c r="E15" s="3">
+        <v>103200</v>
+      </c>
+      <c r="F15" s="3">
         <v>113600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>133400</v>
       </c>
-      <c r="G15" s="3">
-        <v>117800</v>
-      </c>
       <c r="H15" s="3">
-        <v>131800</v>
+        <v>96300</v>
       </c>
       <c r="I15" s="3">
+        <v>109400</v>
+      </c>
+      <c r="J15" s="3">
         <v>965500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>111700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>116600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>109500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>171900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>130200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>140800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>134200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>148200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>167800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>149700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>106000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>148200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>167700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>106700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>157800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>139900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>285500</v>
+        <v>185300</v>
       </c>
       <c r="E17" s="3">
+        <v>239700</v>
+      </c>
+      <c r="F17" s="3">
         <v>340300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>254800</v>
       </c>
-      <c r="G17" s="3">
-        <v>337400</v>
-      </c>
       <c r="H17" s="3">
-        <v>270300</v>
+        <v>286800</v>
       </c>
       <c r="I17" s="3">
+        <v>213600</v>
+      </c>
+      <c r="J17" s="3">
         <v>940300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>247300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>209800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>195400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>417300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>388500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>373700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>167400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>319000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>332500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-279500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-366300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>338200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>375000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>341400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1956800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>422700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>76000</v>
+        <v>118700</v>
       </c>
       <c r="E18" s="3">
+        <v>65500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-17600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>76400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-21500</v>
-      </c>
       <c r="H18" s="3">
-        <v>69000</v>
+        <v>-45000</v>
       </c>
       <c r="I18" s="3">
+        <v>59500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-578500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>80500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>110600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>163300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>407300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>576800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>465000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>619200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>426100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>192100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>675100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>741800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-148600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,378 +1545,394 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>33500</v>
+        <v>-2500</v>
       </c>
       <c r="E20" s="3">
+        <v>33600</v>
+      </c>
+      <c r="F20" s="3">
         <v>25200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3300</v>
-      </c>
       <c r="H20" s="3">
-        <v>14600</v>
+        <v>-2700</v>
       </c>
       <c r="I20" s="3">
+        <v>14200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>15100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-31900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>477200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-141200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>53700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-324100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-376900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-139300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-51300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-22300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>47500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>57300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>37200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>165200</v>
+        <v>242700</v>
       </c>
       <c r="E21" s="3">
+        <v>135000</v>
+      </c>
+      <c r="F21" s="3">
         <v>70800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200600</v>
       </c>
-      <c r="G21" s="3">
-        <v>99500</v>
-      </c>
       <c r="H21" s="3">
-        <v>186200</v>
+        <v>54100</v>
       </c>
       <c r="I21" s="3">
+        <v>154700</v>
+      </c>
+      <c r="J21" s="3">
         <v>389200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>177000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>259200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>260100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1056400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>565900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>659500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>429300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>561700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>685500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>796500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>115800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>177500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E22" s="3">
         <v>22900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>22500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>19500</v>
+        <v>93600</v>
       </c>
       <c r="E23" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-59500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-33600</v>
-      </c>
       <c r="H23" s="3">
-        <v>40900</v>
+        <v>-57600</v>
       </c>
       <c r="I23" s="3">
+        <v>31700</v>
+      </c>
+      <c r="J23" s="3">
         <v>-693000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>136800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>286400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>862000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>411200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>497600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>280200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>397200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-203500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>517000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>671300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-52200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-140000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-119000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>9100</v>
+        <v>39000</v>
       </c>
       <c r="E24" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F24" s="3">
         <v>-46700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13300</v>
       </c>
-      <c r="G24" s="3">
-        <v>26600</v>
-      </c>
       <c r="H24" s="3">
-        <v>39200</v>
+        <v>21900</v>
       </c>
       <c r="I24" s="3">
+        <v>38100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-84800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>40200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>466600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>140100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>135000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>52600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-56400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>65700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>171300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-70000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-47700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-247700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>17000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>10400</v>
+        <v>54500</v>
       </c>
       <c r="E26" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-60200</v>
-      </c>
       <c r="H26" s="3">
-        <v>1700</v>
+        <v>-79500</v>
       </c>
       <c r="I26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="J26" s="3">
         <v>-608100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>42400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>96600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>281100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>395400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>271100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>362600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>284000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>344600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-147100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>451300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-57700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-69900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-71300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-171200</v>
+      </c>
+      <c r="E27" s="3">
         <v>10400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-60200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-608100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>42400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>96600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>281100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>395400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>271100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>362600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>284000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>344600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-147100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>451300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-57700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-69900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-71300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,16 +2236,19 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-225700</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2196,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-33500</v>
+        <v>2500</v>
       </c>
       <c r="E32" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-25200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9200</v>
       </c>
-      <c r="G32" s="3">
-        <v>3300</v>
-      </c>
       <c r="H32" s="3">
-        <v>-14600</v>
+        <v>2700</v>
       </c>
       <c r="I32" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-15100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>31900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-477200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>141200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-53700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>324100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>376900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>139300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>51300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>22300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-47500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-57300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-171200</v>
+      </c>
+      <c r="E33" s="3">
         <v>10400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-60200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-608100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>42400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>96600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>281100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>395400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>271100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>362600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>284000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>344600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-147100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>451300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-57700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-69900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-71300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-171200</v>
+      </c>
+      <c r="E35" s="3">
         <v>10400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-60200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-608100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>42400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>96600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>281100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>395400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>271100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>362600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>284000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>344600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-147100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>451300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-57700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-69900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-71300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E41" s="3">
         <v>16400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>91600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>141300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>195600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>188100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>107100</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="K41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>73800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6000</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
       <c r="S41" s="3">
         <v>0</v>
       </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>3600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2937,8 +3027,8 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>8</v>
@@ -2955,8 +3045,8 @@
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2979,345 +3069,360 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>219700</v>
+      </c>
+      <c r="E43" s="3">
         <v>223400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>207500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>203100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>188900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>269700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>183900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>223000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>217400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>247300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>373700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>391200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>369400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>396700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>328600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>281600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>205900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>240500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>196100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>179400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>233000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>188400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>211400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E44" s="3">
         <v>33800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>28300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>21600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>33200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>43400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>19900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>22700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>30800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>25800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>20100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>22800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>24600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>13400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>21500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>15800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>29400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>28000</v>
+        <v>494900</v>
       </c>
       <c r="E45" s="3">
         <v>28000</v>
       </c>
       <c r="F45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="G45" s="3">
         <v>68500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>71000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>118300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>237600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>195900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>246300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>249300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>307300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>168700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>134200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>126800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>118200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>155800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>58300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>44600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>65800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>83100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>123900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>77900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>859200</v>
+      </c>
+      <c r="E46" s="3">
         <v>354600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>404700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>482000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>541300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>654600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>623600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>485900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>561500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>631200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>714400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>598500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>530100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>551900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>472800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>460100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>292800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>300000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>261000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>267600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>342400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>344700</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>347700</v>
       </c>
       <c r="Z46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E47" s="3">
         <v>54600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>54800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>58700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>58500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>59300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>55500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>50500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>38500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>56400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>38100</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
@@ -3334,8 +3439,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3349,82 +3454,88 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3929700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4470600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3643700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3848300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3790900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3796200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3847300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4644500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4708800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4602200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5962100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5646000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5421300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5175200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5057500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4915500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4816300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4071700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3361200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3352000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3553000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3531500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5301800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>258100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>316300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>292100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>472000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>375000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>374000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>298400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>354800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>486900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>506800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>466700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>496200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>216700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4918500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4928400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4250400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4503600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4517500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4670600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4721900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5293800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5422100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5384400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6991100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6608600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6281600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6199100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5905300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5749600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5407500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4726500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4109100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4126400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4362100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4372300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5866100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,106 +4053,110 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>286800</v>
+      </c>
+      <c r="E57" s="3">
         <v>369800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>287200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>237600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>243300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>284900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>272100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>272500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>323600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>347300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>481400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>444700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>422800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>398900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>440700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>364500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>346500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>312000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>297700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>246700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>309600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>441800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>312400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E58" s="3">
         <v>9000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -4071,304 +4205,319 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E59" s="3">
         <v>120900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>128700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>131100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>232600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>266500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>239100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>269600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>334000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>417200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>410600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>542300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>535800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>655900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>306200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>531500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>181700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>73300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>135500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>84200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>58800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>64500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>103800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>442500</v>
+      </c>
+      <c r="E60" s="3">
         <v>499600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>424400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>386100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>496500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>566600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>527100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>542200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>657600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>764500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>892000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>987100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>958700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1054900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>746800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>896000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>528200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>385300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>433100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>330900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>368400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>506300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>416200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1469400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1343400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>707800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>758800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>736900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>710700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>717100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>741700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>721000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>724200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1132900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1463400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1579300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1436100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1711800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1827400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1841500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1984200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2010400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2153200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2220700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2085300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2017700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>748900</v>
+      </c>
+      <c r="E62" s="3">
         <v>816900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>911000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>946800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>940300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>916400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>893600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>838800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>797300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>743100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1565100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1268100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1062100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1379600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1380600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1290800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1176000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>946500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>740200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>663200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>742300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>628400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>978900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2943500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2923800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2296700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2372800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2449300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2468300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2426200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2446000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2535100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2590900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3590000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3718600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3600100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3870600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3839200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4014300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3545700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3315900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3183700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3147300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3331400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3220000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3412800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1115700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-889200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-895800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-937800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-973600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-926500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-956800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-338600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-380200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-463200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1975000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2004600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1953600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2130800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2068200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2202300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2295600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2847800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2887100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2793500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3401100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2889900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2681500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2328500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2066100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1735400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1861800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1410600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>925400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>979100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1030700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1152300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2453300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-171200</v>
+      </c>
+      <c r="E81" s="3">
         <v>10400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-60200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-608100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>42400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>96600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>281100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>395400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>271100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>362600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>284000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>344600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-147100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>451300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-57700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-69900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-71300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>117800</v>
+      </c>
+      <c r="E83" s="3">
         <v>131800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>196100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>111700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>116600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>109500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>127000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>94800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>109300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>107500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>171900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>130200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>140800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>134200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>148200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>167800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>149700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>106000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>148200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>167700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>106700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>157800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>139900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E89" s="3">
         <v>195100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>147700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>99600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>194600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>261600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>260400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>87600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>131100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>287200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>495200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>447600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>530400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>341100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>250400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>211500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>253400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>119100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>135100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>93800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>278400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>220500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-881200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-143100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-91000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-84800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-140900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-110200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-95200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-127700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-213600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-172900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-186200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-611000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-92100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-172700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-158600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-145900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-873700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-107500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-107900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-111800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-133900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-126000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-124200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-168100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-168300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-612600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-110300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-134900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-162900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-97200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-74700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-50600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-41800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-122000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-187000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-117000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,47 +6715,48 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E96" s="3">
         <v>12900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>13000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>14100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>14000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>12000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>12400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>12100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>12300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>9700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-13000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-10000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -6545,19 +6779,22 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-17400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-100300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-97300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E100" s="3">
         <v>602500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-82000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-72700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-44800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-61800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-34100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-143500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-323000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-272500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>78500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-231400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-108000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-48400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-159900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-47200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-83200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-51200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>118200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-104400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-85200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-75300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-41200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-56800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>83600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>107100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-37500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-37100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>63600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6000</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,365 +656,377 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E8" s="3">
         <v>303000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>304000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>305100</v>
       </c>
-      <c r="G8" s="3">
-        <v>322700</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3">
         <v>269800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>241800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>273200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>361800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>327700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>320500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>358700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>824600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>965300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>838700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>786600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>745100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>524600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>395600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>375500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>320000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>274800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>192800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>353300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>423100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E9" s="3">
         <v>124400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>114800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>98900</v>
       </c>
-      <c r="G9" s="3">
-        <v>113700</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3">
         <v>99900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>97900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>105500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>106700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>119800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>118200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>209400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>178000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>159900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>150600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>139900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>129600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>140000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>138500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>114100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>115300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>177200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>185500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E10" s="3">
         <v>178600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>189100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>206300</v>
       </c>
-      <c r="G10" s="3">
-        <v>209000</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3">
         <v>169900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>143900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>174100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>256300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>221000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>240600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>638100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>755900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>660700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>626700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>594500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>384700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>266000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>235500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>181500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>160700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>77500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>176100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>237600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1136,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,13 +1219,16 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>417300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1229,21 +1248,21 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>99300</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-9500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-152000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1251,120 +1270,126 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-192100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-23900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-22200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-610800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-662900</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>47800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>69700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1564900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>46100</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E15" s="3">
         <v>124900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>121500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>103200</v>
       </c>
-      <c r="G15" s="3">
-        <v>113600</v>
-      </c>
       <c r="H15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="I15" s="3">
         <v>113100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>96300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>109400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>965500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>111700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>116600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>109500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>171900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>130200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>140800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>134200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>148200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>167800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>149700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>106000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>148200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>167700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>106700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>157800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>139900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>258900</v>
+      </c>
+      <c r="E17" s="3">
         <v>232600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>185300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>239700</v>
       </c>
-      <c r="G17" s="3">
-        <v>340300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3">
         <v>205800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>286800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>213600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>940300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>247300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>209800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>195400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>417300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>388500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>373700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>167400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>319000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>332500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-279500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-366300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>338200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>375000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>341400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1956800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>422700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E18" s="3">
         <v>70500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>118700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>65500</v>
       </c>
-      <c r="G18" s="3">
-        <v>-17600</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3">
         <v>64000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-45000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>59500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-578500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>80500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>110600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>163300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>407300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>576800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>465000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>619200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>426100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>192100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>675100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>741800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-18200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-148600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,408 +1612,424 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E20" s="3">
         <v>30100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33600</v>
       </c>
-      <c r="G20" s="3">
-        <v>25200</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3">
         <v>9300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>14200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>15100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-31900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>477200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-141200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>53700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-324100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-376900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-139300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-51300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-14200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>47500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>57300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>37200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>234900</v>
+      </c>
+      <c r="E21" s="3">
         <v>165300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>242700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>135000</v>
       </c>
-      <c r="G21" s="3">
-        <v>70800</v>
-      </c>
       <c r="H21" s="3">
+        <v>38300</v>
+      </c>
+      <c r="I21" s="3">
         <v>167900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>54100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>154700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>389200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>177000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>259200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>260100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1056400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>565900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>659500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>429300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>561700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>685500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>796500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>115800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>177500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E22" s="3">
         <v>24700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22900</v>
       </c>
-      <c r="G22" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
         <v>15700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>22500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-355200</v>
+      </c>
+      <c r="E23" s="3">
         <v>15700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>93600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-59500</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3">
         <v>39100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-57600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-693000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>50400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>136800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>286400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>862000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>411200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>497600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>280200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>397200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-203500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>517000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>671300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-52200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-140000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>18400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E24" s="3">
         <v>19100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6300</v>
       </c>
-      <c r="G24" s="3">
-        <v>-46700</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3">
         <v>9600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>38100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-84800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>466600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>140100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>135000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>52600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-56400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>65700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>171300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-47700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-247700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>17000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-319500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>54500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3">
         <v>29500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-79500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-608100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>42400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>96600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>281100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>395400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>271100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>362600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>284000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>344600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-147100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>451300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-57700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-71300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-319200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-171200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
         <v>38300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-60200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-608100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>96600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>281100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>395400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>271100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>362600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>284000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>344600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-147100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>451300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>500000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-57700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-71300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,35 +2357,38 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>300</v>
+      </c>
+      <c r="E29" s="3">
         <v>5300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-225700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>7800</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>8800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>19300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>8100</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
@@ -2380,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2606,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-30100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-25200</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3">
         <v>-9300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-14200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-15100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>31900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-477200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>141200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-53700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>324100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>376900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>139300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>51300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>14200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>22300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-47500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-57300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-319200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-171200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3">
         <v>38300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-60200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-608100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>96600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>281100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>395400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>271100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>362600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>284000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>344600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-147100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>451300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>500000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-57700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-71300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-319200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-171200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3">
         <v>38300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-60200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-608100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>96600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>281100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>395400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>271100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>362600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>284000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>344600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-147100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>451300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>500000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-57700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-71300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3090,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E41" s="3">
         <v>33100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>91600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>141300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>195600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>188100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>107100</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="M41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>73800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6000</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>29000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3123,8 +3212,8 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
@@ -3141,8 +3230,8 @@
       <c r="T42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3165,375 +3254,390 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>199500</v>
+      </c>
+      <c r="E43" s="3">
         <v>141100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>219700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>223400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>207500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>203100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>188900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>269700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>183900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>223000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>217400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>247300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>373700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>391200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>369400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>396700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>328600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>281600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>205900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>240500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>196100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>179400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>233000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>188400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>211400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E44" s="3">
         <v>32500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>46100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>33800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>28300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>21600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>33200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>43400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>19900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>22700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>30800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>25800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>23900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>20100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>22800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>28500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>24600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>21500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>15800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>29400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E45" s="3">
         <v>32000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>494900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>28000</v>
       </c>
       <c r="G45" s="3">
         <v>28000</v>
       </c>
       <c r="H45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I45" s="3">
         <v>68500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>71000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>118300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>237600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>195900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>246300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>249300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>307300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>168700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>134200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>126800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>118200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>155800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>58300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>65800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>83100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>123900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>77900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>340800</v>
+      </c>
+      <c r="E46" s="3">
         <v>283300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>859200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>354600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>404700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>482000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>541300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>654600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>623600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>485900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>561500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>631200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>714400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>598500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>530100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>551900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>472800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>460100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>292800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>300000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>261000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>267600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>342400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>344700</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>347700</v>
       </c>
       <c r="AB46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E47" s="3">
         <v>54900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>56600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>54600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>54800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>58700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>58500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>59300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>55500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>50500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>56400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>38100</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
@@ -3550,8 +3654,8 @@
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3565,88 +3669,94 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3492600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3882100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3929700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4470600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3643700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3848300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3790900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3796200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3847300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4644500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4708800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4602200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5962100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5646000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5421300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5175200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5057500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4915500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4816300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4071700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3361200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3352000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3553000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3531500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5301800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3725,8 +3835,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4001,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E52" s="3">
         <v>10500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>44300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>258100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>316300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>292100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>472000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>375000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>374000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>298400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>354800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>486900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>506800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>466700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>496200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>216700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4167,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3897700</v>
+      </c>
+      <c r="E54" s="3">
         <v>4274200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4918500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4928400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4250400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4503600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4517500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4670600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4721900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5293800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5422100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5384400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6991100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6608600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6281600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6199100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5905300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5749600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5407500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4726500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4109100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4126400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4362100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4372300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5866100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,118 +4314,122 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>336600</v>
+      </c>
+      <c r="E57" s="3">
         <v>289000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>286800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>369800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>287200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>237600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>243300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>284900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>272100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>272500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>323600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>347300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>481400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>444700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>422800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>398900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>440700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>364500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>346500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>312000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>297700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>246700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>309600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>441800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>312400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>16000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4345,328 +4478,343 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E59" s="3">
         <v>55100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>146600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>120900</v>
       </c>
-      <c r="G59" s="3">
-        <v>128700</v>
-      </c>
       <c r="H59" s="3">
+        <v>165900</v>
+      </c>
+      <c r="I59" s="3">
         <v>131100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>232600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>266500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>239100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>269600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>334000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>417200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>410600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>542300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>535800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>655900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>306200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>531500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>181700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>73300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>135500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>84200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>58800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>64500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>103800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>404400</v>
+      </c>
+      <c r="E60" s="3">
         <v>351400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>442500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>499600</v>
       </c>
-      <c r="G60" s="3">
-        <v>424400</v>
-      </c>
       <c r="H60" s="3">
+        <v>461600</v>
+      </c>
+      <c r="I60" s="3">
         <v>386100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>496500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>566600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>527100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>542200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>657600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>764500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>892000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>987100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>958700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1054900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>746800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>896000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>528200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>385300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>433100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>330900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>368400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>506300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>416200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>942800</v>
+      </c>
+      <c r="E61" s="3">
         <v>944200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1469400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1343400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>707800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>758800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>736900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>710700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>717100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>741700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>721000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>724200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1132900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1463400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1579300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1436100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1711800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1827400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1841500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1984200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2010400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2153200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2220700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2085300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2017700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>698800</v>
+      </c>
+      <c r="E62" s="3">
         <v>751100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>748900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>816900</v>
       </c>
-      <c r="G62" s="3">
-        <v>911000</v>
-      </c>
       <c r="H62" s="3">
+        <v>873700</v>
+      </c>
+      <c r="I62" s="3">
         <v>946800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>940300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>916400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>893600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>838800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>797300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>743100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1565100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1268100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1062100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1379600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1380600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1290800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1176000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>946500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>740200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>663200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>742300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>628400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>978900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5059,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2277200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2329900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2943500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2923800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2296700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2372800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2449300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2468300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2426200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2446000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2535100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2590900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3590000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3718600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3600100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3870600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3839200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4014300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3545700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3315900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3183700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3147300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3331400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3220000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3412800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5505,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1444300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1098700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1115700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-889200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-895800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-937800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-973600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-926500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-956800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-338600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-380200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-463200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5837,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1620500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1944300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1975000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2004600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1953600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2130800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2068200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2202300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2295600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2847800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2887100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2793500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3401100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2889900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2681500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2328500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2066100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1735400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1861800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1410600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>925400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>979100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1030700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1152300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2453300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-319200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-171200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-12700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3">
         <v>38300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-60200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-608100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>96600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>281100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>395400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>271100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>362600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>284000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>344600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-147100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>451300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>500000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-57700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-69900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-71300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6207,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>133400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>117800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>131800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>196100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>111700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>116600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>109500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>127000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>94800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>109300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>107500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>171900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>130200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>140800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>134200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>148200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>167800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>149700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>106000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>148200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>167700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>106700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>157800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>139900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E89" s="3">
         <v>279600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>103000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>195100</v>
       </c>
-      <c r="G89" s="3">
-        <v>147700</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>99600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>194600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>261600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>260400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>87600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>131100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>287200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>495200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>447600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>530400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>341100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>250400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>211500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>253400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>119100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>135100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>93800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>278400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>220500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,88 +6819,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>653000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-105300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-85800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-881200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-143100</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-91000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-84800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-140900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-110200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-95200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-127700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-213600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-172900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-186200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-611000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-92100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-172700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-158600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="E94" s="3">
         <v>233400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-145900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-873700</v>
       </c>
-      <c r="G94" s="3">
-        <v>-107500</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-107900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-111800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-133900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-126000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-124200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-80300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-168100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-168300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-612600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-110300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-134900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-162900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-97200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-74700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-50600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-41800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-122000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-187000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-117000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,53 +7182,54 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E96" s="3">
         <v>14400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>14700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>12900</v>
       </c>
-      <c r="G96" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>14100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>14000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>12000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>12400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>12100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>12300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>9700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-13000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -7019,19 +7252,22 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-100300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-97300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,244 +7512,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-530100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>76400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>602500</v>
       </c>
-      <c r="G100" s="3">
-        <v>-82000</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-48700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-72700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-44800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-61800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-34100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-143500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-323000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-272500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>78500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-231400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-108000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-48400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-159900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-47200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-83200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-51200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>118200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-104400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-85200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>33500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-75300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-41200</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-56800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>83600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>107100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-37500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-37100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>63600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6000</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VET_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>VET</t>
   </si>
@@ -656,377 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>345400</v>
+      </c>
+      <c r="E8" s="3">
         <v>311000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>303000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>304000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>305100</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>269800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>241800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>273200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>361800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>327700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>320500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>358700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>824600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>965300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>838700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>786600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>745100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>524600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>395600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>375500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>320000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>274800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>192800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>353300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>423100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>391900</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E9" s="3">
         <v>123500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>124400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>114800</v>
       </c>
-      <c r="G9" s="3">
-        <v>98900</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="3">
+        <v>98800</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>97900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>99000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>105500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>106700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>119800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>118200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>186500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>209400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>178000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>159900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>150600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>139900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>129600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>140000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>138500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>114100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>115300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>177200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>185500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>146600</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E10" s="3">
         <v>187500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>178600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>189100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>206300</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>169900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>143900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>174100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>256300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>221000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>240600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>638100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>755900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>660700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>626700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>594500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>384700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>266000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>235500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>181500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>160700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>77500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>176100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>237600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,16 +1239,19 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>417300</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1251,21 +1271,21 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>99300</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-9500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-152000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1273,123 +1293,129 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-192100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-23900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-22200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-610800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-662900</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>47800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>69700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1564900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>46100</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E15" s="3">
         <v>152700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>124900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>121500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>103200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>96300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>965500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>111700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>116600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>109500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>171900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>130200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>140800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>134200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>148200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>167800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>149700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>106000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>148200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>167700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>106700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>157800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>139900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>488500</v>
+      </c>
+      <c r="E17" s="3">
         <v>258900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>232600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>185300</v>
       </c>
-      <c r="G17" s="3">
-        <v>239700</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="3">
+        <v>239600</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>205800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>286800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>213600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>940300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>247300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>209800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>195400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>417300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>388500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>373700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>167400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>319000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>332500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-279500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-366300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>338200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>375000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>341400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1956800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>422700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>378000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-143200</v>
+      </c>
+      <c r="E18" s="3">
         <v>52100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>70500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>118700</v>
       </c>
-      <c r="G18" s="3">
-        <v>65500</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="3">
+        <v>65600</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>64000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-45000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>59500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-578500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>80500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>110600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>163300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>407300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>576800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>465000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>619200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>426100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>192100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>675100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>741800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-148600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1603500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,423 +1646,439 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-30200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>30100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>33600</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>14200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>15100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-31900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>477200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-141200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>53700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-324100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-376900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-139300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-51300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>47500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>57300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>37200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-36900</v>
+      </c>
+      <c r="E21" s="3">
         <v>234900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>165300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>242700</v>
       </c>
-      <c r="G21" s="3">
-        <v>135000</v>
-      </c>
       <c r="H21" s="3">
+        <v>135200</v>
+      </c>
+      <c r="I21" s="3">
         <v>38300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>167900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>54100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>154700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>389200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>177000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>259200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>260100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1056400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>565900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>659500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>429300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>561700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-17000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>685500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>796500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>115800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>45200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1388400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>177500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>188700</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E22" s="3">
         <v>20200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>24700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22900</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>22500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-173600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-355200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>93600</v>
       </c>
-      <c r="G23" s="3">
-        <v>8900</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>39100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-57600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-693000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>50400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>136800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>286400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>862000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>411200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>497600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>280200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>397200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-203500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>517000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>671300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-52200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-140000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-119000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1566200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-35700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39000</v>
       </c>
-      <c r="G24" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-84800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>466600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>140100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>135000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>52600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-56400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>65700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>171300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-47700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-247700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>17000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-101200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-319500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>54500</v>
       </c>
-      <c r="G26" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-79500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-608100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>96600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>281100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>395400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>271100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>362600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>284000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>344600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-147100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>451300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-319200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-171200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10400</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>38300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-60200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-608100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>96600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>281100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>395400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>271100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>362600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>284000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>344600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-147100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>451300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,38 +2418,41 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E29" s="3">
         <v>300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>5300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-225700</v>
       </c>
-      <c r="G29" s="3">
-        <v>7800</v>
-      </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>8800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>19300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>8100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2443,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2676,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E32" s="3">
         <v>30200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-30100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-33600</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-14200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-15100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>31900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-477200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>141200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-53700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>324100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>376900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>139300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>51300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>22300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-47500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-57300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-319200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-171200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10400</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="I33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>38300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-60200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-608100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>96600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>281100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>395400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>271100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>362600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>284000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>344600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-147100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>451300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-319200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-171200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10400</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="I35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>38300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-60200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-608100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>96600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>281100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>395400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>271100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>362600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>284000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>344600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-147100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>451300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,91 +3177,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E41" s="3">
         <v>13900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>50700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>91600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>141300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>195600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>188100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>107100</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="N41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>73800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6000</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>16600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>29000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3215,8 +3305,8 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>8</v>
@@ -3233,8 +3323,8 @@
       <c r="U42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3257,390 +3347,405 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>199900</v>
+      </c>
+      <c r="E43" s="3">
         <v>199500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>141100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>219700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>223400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>207500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>203100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>188900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>269700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>183900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>223000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>217400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>247300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>373700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>391200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>369400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>396700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>328600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>281600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>205900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>240500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>196100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>179400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>233000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>188400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>211400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>246500</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E44" s="3">
         <v>34000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>46100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>33800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>28300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>21600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>33200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>43400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>19900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>16100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>19700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>30800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>25800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>23900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>20100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>22800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>28500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>24600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>13400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>17100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>21500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>15800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>29400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E45" s="3">
         <v>57400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>494900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>28000</v>
       </c>
       <c r="H45" s="3">
         <v>28000</v>
       </c>
       <c r="I45" s="3">
+        <v>28000</v>
+      </c>
+      <c r="J45" s="3">
         <v>68500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>71000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>118300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>237600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>195900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>246300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>249300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>307300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>168700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>134200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>126800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>118200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>155800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>58300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>65800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>83100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>123900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>77900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>74800</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>347300</v>
+      </c>
+      <c r="E46" s="3">
         <v>340800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>283300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>859200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>354600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>404700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>482000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>541300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>654600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>623600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>485900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>561500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>631200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>714400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>598500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>530100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>551900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>472800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>460100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>292800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>300000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>261000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>267600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>342400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>344700</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>347700</v>
       </c>
       <c r="AC46" s="3">
         <v>347700</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>347700</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E47" s="3">
         <v>32000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>54900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>56600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>54600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>54800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>58700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>58500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>59300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>55500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>50500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>38500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>56400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>47800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>38100</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
@@ -3657,8 +3762,8 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3672,91 +3777,97 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3497700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3492600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3882100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3929700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4470600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3643700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3848300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3790900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3796200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3847300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4644500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4708800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4602200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5962100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5646000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5421300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5175200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5057500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4915500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4816300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4071700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3361200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3352000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3553000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3531500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5301800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5389800</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3838,8 +3949,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,91 +4121,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E52" s="3">
         <v>18400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>258100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>316300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>292100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>472000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>375000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>374000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>298400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>354800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>486900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>506800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>466700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>496200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>216700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>221600</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3973600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3897700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4274200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4918500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4928400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4250400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4503600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4517500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4670600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4721900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5293800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5422100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5384400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6991100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6608600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6281600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6199100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5905300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5749600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5407500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4726500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4109100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4126400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4362100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4372300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5866100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5959100</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,124 +4445,128 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>305800</v>
+      </c>
+      <c r="E57" s="3">
         <v>336600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>289000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>286800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>369800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>287200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>237600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>243300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>284900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>272100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>272500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>323600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>347300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>481400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>444700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>422800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>398900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>440700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>364500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>346500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>312000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>297700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>246700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>309600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>441800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>312400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>310600</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>16000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4481,340 +4615,355 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>236400</v>
+      </c>
+      <c r="E59" s="3">
         <v>61100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>146600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>120900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>165900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>131100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>232600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>266500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>239100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>269600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>334000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>417200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>410600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>542300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>535800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>655900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>306200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>531500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>181700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>73300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>135500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>84200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>58800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>64500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>103800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>548100</v>
+      </c>
+      <c r="E60" s="3">
         <v>404400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>351400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>442500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>499600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>461600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>386100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>496500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>566600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>527100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>542200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>657600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>764500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>892000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>987100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>958700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1054900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>746800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>896000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>528200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>385300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>433100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>330900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>368400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>506300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>416200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>395100</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>933600</v>
+      </c>
+      <c r="E61" s="3">
         <v>942800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>944200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1469400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1343400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>707800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>758800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>736900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>710700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>717100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>741700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>721000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>724200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1132900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1463400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1579300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1436100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1711800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1827400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1841500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1984200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2010400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2153200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2220700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2085300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2017700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2052800</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>813000</v>
+      </c>
+      <c r="E62" s="3">
         <v>698800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>751100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>748900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>816900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>873700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>946800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>940300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>916400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>893600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>838800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>797300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>743100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1565100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1268100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1062100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1379600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1380600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1290800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1176000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>946500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>740200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>663200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>742300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>628400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>978900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>977200</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2508800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2277200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2329900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2943500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2923800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2296700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2372800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2449300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2468300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2426200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2446000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2535100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2590900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3590000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3718600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3600100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3870600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3839200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4014300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3545700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3315900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3183700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3147300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3331400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3220000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3412800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3425100</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5425,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1534700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1444300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1098700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1115700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-889200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-895800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-937800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-973600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-926500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-956800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-338600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-380200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-463200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1001700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1383700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1979400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2253600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2597800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2450700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-2900000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3400000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-3342200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3272300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3199600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1791000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1684500</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1464800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1620500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1944300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1975000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2004600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1953600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2130800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2068200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2202300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2295600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2847800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2887100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2793500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3401100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2889900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2681500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2328500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2066100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1735400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1861800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1410600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>925400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>979100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1030700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1152300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2453300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2534100</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-104300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-319200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-171200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10400</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="I81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>38300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-60200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-608100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>96600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>281100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>395400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>271100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>362600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>284000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>344600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-147100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>451300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-69900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1318500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,91 +6406,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>122700</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>133400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>117800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>131800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>196100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>111700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>116600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>109500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>127000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>94800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>109300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>107500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>171900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>130200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>140800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>134200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>148200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>167800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>149700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>106000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>148200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>167700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>106700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>157800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>139900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>162900</v>
+      </c>
+      <c r="E89" s="3">
         <v>97300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>279600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>103000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>195100</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>99600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>194600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>261600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>260400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>87600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>131100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>287200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>495200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>447600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>530400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>341100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>250400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>211500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>253400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>119100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>135100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>93800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>278400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>220500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,91 +7040,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>653000</v>
+        <v>-96400</v>
       </c>
       <c r="E91" s="3">
-        <v>-105300</v>
+        <v>-139900</v>
       </c>
       <c r="F91" s="3">
-        <v>-85800</v>
+        <v>-104500</v>
       </c>
       <c r="G91" s="3">
-        <v>-881200</v>
-      </c>
-      <c r="H91" s="3" t="s">
+        <v>-84700</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-126700</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I91" s="3">
-        <v>-91000</v>
-      </c>
       <c r="J91" s="3">
+        <v>-89800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-84800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-140900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-110200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-95200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-127700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-213600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-172900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-186200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-611000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-92100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-172700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-158600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7100</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-135200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-79500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>233400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-145900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-873700</v>
       </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-107900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-111800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-133900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-126000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-124200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-80300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-168100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-168300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-612600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-110300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-134900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-162900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-97200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-74700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-50600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-41800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-122000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-187000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-164000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,56 +7416,57 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E96" s="3">
         <v>29100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>14400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>14700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>12900</v>
       </c>
-      <c r="H96" s="3" t="s">
+      <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>14100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>14000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>12000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>12400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>12100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>12300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>9700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-10000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7255,19 +7489,22 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-17400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-100300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-97300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-98200</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,253 +7758,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-37100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-530100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>76400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>602500</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-48700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-72700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-44800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-61800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-143500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-323000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-272500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>78500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-231400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-108000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-48400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-159900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-47200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-83200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-51200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>118200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-104400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-85200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>33500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-75300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-56800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>83600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>107100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-37500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-37100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6000</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
         <v>-3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-12400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24800</v>
       </c>
     </row>
